--- a/thaco/color/BANG LUONG MAU 1 05-01-2026 05_24_47_820.xlsx
+++ b/thaco/color/BANG LUONG MAU 1 05-01-2026 05_24_47_820.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vnphngqu/Library/Mobile Documents/com~apple~CloudDocs/THACO x IADC/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/adity/Documents/GitHub/gitlocal/thaco/color/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869ADEAE-24D4-3B49-900A-687A377E9786}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0DC441-A2AC-8440-9FC6-B5D26B9894C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="780" windowWidth="34320" windowHeight="15720" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
+    <workbookView xWindow="38540" yWindow="660" windowWidth="38100" windowHeight="20800" tabRatio="761" xr2:uid="{D2D6ECD8-DC99-4D28-8DAC-0623419D46D2}"/>
   </bookViews>
   <sheets>
     <sheet name="Bảng lương CB-NV" sheetId="1" r:id="rId1"/>
@@ -4273,7 +4273,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -4290,16 +4289,33 @@
   <commentList>
     <comment ref="E8" authorId="0" shapeId="0" xr:uid="{3B7FFEF4-AE63-4DFA-B536-7BAA2BEE4A14}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     TV: Thử việc
 CT: Chính thức</t>
+        </r>
       </text>
     </comment>
     <comment ref="F8" authorId="1" shapeId="0" xr:uid="{F2CA1CEE-0407-4ECA-B543-A94DFE1E09BB}">
       <text>
-        <t xml:space="preserve">[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Đối tượng Lương ngày tại các TĐTV
@@ -4307,6 +4323,7 @@
     LT: Lương Tháng
 LN: Lương ngày
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -4322,19 +4339,37 @@
   <commentList>
     <comment ref="E5" authorId="0" shapeId="0" xr:uid="{E2E9D45B-DF17-427F-97F4-573038627707}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     TV: Thử việc
 CT: Chính thức</t>
+        </r>
       </text>
     </comment>
     <comment ref="F5" authorId="1" shapeId="0" xr:uid="{71B14A45-6C96-40CB-98DD-DD6B3885D55F}">
       <text>
-        <t>[Threaded comment]
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
 Comment:
     Đối tượng Lương ngày tại các TĐTV</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -6184,6 +6219,171 @@
     <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6193,21 +6393,6 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6253,15 +6438,6 @@
     <xf numFmtId="164" fontId="8" fillId="2" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="165" fontId="22" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6286,146 +6462,11 @@
     <xf numFmtId="165" fontId="22" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="28" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="20" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="43" fontId="24" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="10" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="18" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="22" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6436,6 +6477,21 @@
     <xf numFmtId="165" fontId="22" fillId="3" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="22" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -6457,26 +6513,29 @@
     <xf numFmtId="43" fontId="22" fillId="2" borderId="17" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -6486,30 +6545,6 @@
     </xf>
     <xf numFmtId="165" fontId="23" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="27" fillId="4" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -6520,7 +6555,7 @@
     <cellStyle name="Comma 21" xfId="5" xr:uid="{3FE22722-219A-4172-A93A-8D6EF52AB3B5}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="7" xr:uid="{2A744030-9AE7-4BB8-BAD0-3C0C8A2953B6}"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="2" builtinId="5"/>
     <cellStyle name="Percent 2" xfId="8" xr:uid="{2763F245-BD58-41B8-A450-D1B9FA8F507A}"/>
   </cellStyles>
   <dxfs count="24">
@@ -6785,9 +6820,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -6825,7 +6860,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -6931,7 +6966,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -7073,7 +7108,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -7312,91 +7347,91 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="316" t="str">
+      <c r="A3" s="262" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="316"/>
-      <c r="C3" s="316"/>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="316"/>
-      <c r="K3" s="316"/>
-      <c r="L3" s="316"/>
-      <c r="M3" s="316"/>
-      <c r="N3" s="316"/>
-      <c r="O3" s="316"/>
-      <c r="P3" s="316"/>
-      <c r="Q3" s="316"/>
-      <c r="R3" s="316"/>
-      <c r="S3" s="316"/>
-      <c r="T3" s="316"/>
-      <c r="U3" s="316"/>
-      <c r="V3" s="316"/>
-      <c r="W3" s="316"/>
-      <c r="X3" s="316"/>
-      <c r="Y3" s="316"/>
-      <c r="Z3" s="316"/>
-      <c r="AA3" s="316"/>
-      <c r="AB3" s="316"/>
-      <c r="AC3" s="316"/>
-      <c r="AD3" s="316"/>
-      <c r="AE3" s="316"/>
-      <c r="AF3" s="316"/>
-      <c r="AG3" s="316"/>
-      <c r="AH3" s="316"/>
-      <c r="AI3" s="316"/>
-      <c r="AJ3" s="316"/>
-      <c r="AK3" s="316"/>
-      <c r="AL3" s="316"/>
-      <c r="AM3" s="316"/>
-      <c r="AN3" s="316"/>
-      <c r="AO3" s="316"/>
-      <c r="AP3" s="316"/>
-      <c r="AQ3" s="316"/>
-      <c r="AR3" s="316"/>
-      <c r="AS3" s="316"/>
-      <c r="AT3" s="316"/>
-      <c r="AU3" s="316"/>
-      <c r="AV3" s="316"/>
-      <c r="AW3" s="316"/>
-      <c r="AX3" s="316"/>
-      <c r="AY3" s="316"/>
-      <c r="AZ3" s="316"/>
-      <c r="BA3" s="316"/>
-      <c r="BB3" s="316"/>
-      <c r="BC3" s="316"/>
-      <c r="BD3" s="316"/>
-      <c r="BE3" s="316"/>
-      <c r="BF3" s="316"/>
-      <c r="BG3" s="316"/>
-      <c r="BH3" s="316"/>
-      <c r="BI3" s="316"/>
-      <c r="BJ3" s="316"/>
-      <c r="BK3" s="316"/>
-      <c r="BL3" s="316"/>
-      <c r="BM3" s="316"/>
-      <c r="BN3" s="316"/>
-      <c r="BO3" s="316"/>
-      <c r="BP3" s="316"/>
-      <c r="BQ3" s="316"/>
-      <c r="BR3" s="316"/>
-      <c r="BS3" s="316"/>
-      <c r="BT3" s="316"/>
-      <c r="BU3" s="316"/>
+      <c r="B3" s="262"/>
+      <c r="C3" s="262"/>
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="262"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
+      <c r="AA3" s="262"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="262"/>
+      <c r="AF3" s="262"/>
+      <c r="AG3" s="262"/>
+      <c r="AH3" s="262"/>
+      <c r="AI3" s="262"/>
+      <c r="AJ3" s="262"/>
+      <c r="AK3" s="262"/>
+      <c r="AL3" s="262"/>
+      <c r="AM3" s="262"/>
+      <c r="AN3" s="262"/>
+      <c r="AO3" s="262"/>
+      <c r="AP3" s="262"/>
+      <c r="AQ3" s="262"/>
+      <c r="AR3" s="262"/>
+      <c r="AS3" s="262"/>
+      <c r="AT3" s="262"/>
+      <c r="AU3" s="262"/>
+      <c r="AV3" s="262"/>
+      <c r="AW3" s="262"/>
+      <c r="AX3" s="262"/>
+      <c r="AY3" s="262"/>
+      <c r="AZ3" s="262"/>
+      <c r="BA3" s="262"/>
+      <c r="BB3" s="262"/>
+      <c r="BC3" s="262"/>
+      <c r="BD3" s="262"/>
+      <c r="BE3" s="262"/>
+      <c r="BF3" s="262"/>
+      <c r="BG3" s="262"/>
+      <c r="BH3" s="262"/>
+      <c r="BI3" s="262"/>
+      <c r="BJ3" s="262"/>
+      <c r="BK3" s="262"/>
+      <c r="BL3" s="262"/>
+      <c r="BM3" s="262"/>
+      <c r="BN3" s="262"/>
+      <c r="BO3" s="262"/>
+      <c r="BP3" s="262"/>
+      <c r="BQ3" s="262"/>
+      <c r="BR3" s="262"/>
+      <c r="BS3" s="262"/>
+      <c r="BT3" s="262"/>
+      <c r="BU3" s="262"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="297" t="s">
+      <c r="BW3" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="297"/>
-      <c r="BY3" s="297"/>
-      <c r="BZ3" s="297"/>
-      <c r="CA3" s="297"/>
-      <c r="CB3" s="298"/>
+      <c r="BX3" s="275"/>
+      <c r="BY3" s="275"/>
+      <c r="BZ3" s="275"/>
+      <c r="CA3" s="275"/>
+      <c r="CB3" s="276"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="240" t="s">
@@ -7480,12 +7515,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="298"/>
-      <c r="BX4" s="298"/>
-      <c r="BY4" s="298"/>
-      <c r="BZ4" s="298"/>
-      <c r="CA4" s="298"/>
-      <c r="CB4" s="298"/>
+      <c r="BW4" s="276"/>
+      <c r="BX4" s="276"/>
+      <c r="BY4" s="276"/>
+      <c r="BZ4" s="276"/>
+      <c r="CA4" s="276"/>
+      <c r="CB4" s="276"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -7563,12 +7598,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="298"/>
-      <c r="BX5" s="298"/>
-      <c r="BY5" s="298"/>
-      <c r="BZ5" s="298"/>
-      <c r="CA5" s="298"/>
-      <c r="CB5" s="298"/>
+      <c r="BW5" s="276"/>
+      <c r="BX5" s="276"/>
+      <c r="BY5" s="276"/>
+      <c r="BZ5" s="276"/>
+      <c r="CA5" s="276"/>
+      <c r="CB5" s="276"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -7646,12 +7681,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="297"/>
-      <c r="BX6" s="297"/>
-      <c r="BY6" s="297"/>
-      <c r="BZ6" s="297"/>
-      <c r="CA6" s="297"/>
-      <c r="CB6" s="298"/>
+      <c r="BW6" s="275"/>
+      <c r="BX6" s="275"/>
+      <c r="BY6" s="275"/>
+      <c r="BZ6" s="275"/>
+      <c r="CA6" s="275"/>
+      <c r="CB6" s="276"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -7739,356 +7774,356 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="299" t="s">
+      <c r="A8" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="302" t="s">
+      <c r="B8" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="245" t="s">
+      <c r="C8" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="305" t="s">
+      <c r="D8" s="272" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="305" t="s">
+      <c r="E8" s="272" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="245" t="s">
+      <c r="F8" s="256" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="308" t="s">
+      <c r="G8" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="276" t="s">
+      <c r="H8" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="276" t="s">
+      <c r="I8" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="308" t="s">
+      <c r="J8" s="253" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="279" t="s">
+      <c r="K8" s="288" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="280"/>
-      <c r="P8" s="280"/>
-      <c r="Q8" s="280"/>
-      <c r="R8" s="280"/>
-      <c r="S8" s="280"/>
-      <c r="T8" s="280"/>
-      <c r="U8" s="280"/>
-      <c r="V8" s="280"/>
-      <c r="W8" s="280"/>
-      <c r="X8" s="280"/>
-      <c r="Y8" s="281" t="s">
+      <c r="L8" s="289"/>
+      <c r="M8" s="289"/>
+      <c r="N8" s="289"/>
+      <c r="O8" s="289"/>
+      <c r="P8" s="289"/>
+      <c r="Q8" s="289"/>
+      <c r="R8" s="289"/>
+      <c r="S8" s="289"/>
+      <c r="T8" s="289"/>
+      <c r="U8" s="289"/>
+      <c r="V8" s="289"/>
+      <c r="W8" s="289"/>
+      <c r="X8" s="289"/>
+      <c r="Y8" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="282"/>
-      <c r="AA8" s="282"/>
-      <c r="AB8" s="282"/>
-      <c r="AC8" s="282"/>
-      <c r="AD8" s="282"/>
-      <c r="AE8" s="282"/>
-      <c r="AF8" s="282"/>
-      <c r="AG8" s="282"/>
-      <c r="AH8" s="282"/>
-      <c r="AI8" s="282"/>
-      <c r="AJ8" s="282"/>
-      <c r="AK8" s="282"/>
-      <c r="AL8" s="282"/>
-      <c r="AM8" s="282"/>
-      <c r="AN8" s="282"/>
-      <c r="AO8" s="283"/>
-      <c r="AP8" s="308" t="s">
+      <c r="Z8" s="291"/>
+      <c r="AA8" s="291"/>
+      <c r="AB8" s="291"/>
+      <c r="AC8" s="291"/>
+      <c r="AD8" s="291"/>
+      <c r="AE8" s="291"/>
+      <c r="AF8" s="291"/>
+      <c r="AG8" s="291"/>
+      <c r="AH8" s="291"/>
+      <c r="AI8" s="291"/>
+      <c r="AJ8" s="291"/>
+      <c r="AK8" s="291"/>
+      <c r="AL8" s="291"/>
+      <c r="AM8" s="291"/>
+      <c r="AN8" s="291"/>
+      <c r="AO8" s="292"/>
+      <c r="AP8" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="308" t="s">
+      <c r="AQ8" s="253" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="308" t="s">
+      <c r="AR8" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="308" t="s">
+      <c r="AS8" s="253" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="308" t="s">
+      <c r="AT8" s="253" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="308" t="s">
+      <c r="AU8" s="253" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="245" t="s">
+      <c r="AV8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="245" t="s">
+      <c r="AW8" s="256" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="245" t="s">
+      <c r="AX8" s="256" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="313" t="s">
+      <c r="AY8" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="314"/>
-      <c r="BA8" s="314"/>
-      <c r="BB8" s="314"/>
-      <c r="BC8" s="314"/>
-      <c r="BD8" s="314"/>
-      <c r="BE8" s="314"/>
-      <c r="BF8" s="314"/>
-      <c r="BG8" s="314"/>
-      <c r="BH8" s="314"/>
-      <c r="BI8" s="314"/>
-      <c r="BJ8" s="314"/>
-      <c r="BK8" s="314"/>
-      <c r="BL8" s="314"/>
-      <c r="BM8" s="314"/>
-      <c r="BN8" s="314"/>
-      <c r="BO8" s="314"/>
-      <c r="BP8" s="314"/>
-      <c r="BQ8" s="315"/>
-      <c r="BR8" s="268" t="s">
+      <c r="AZ8" s="260"/>
+      <c r="BA8" s="260"/>
+      <c r="BB8" s="260"/>
+      <c r="BC8" s="260"/>
+      <c r="BD8" s="260"/>
+      <c r="BE8" s="260"/>
+      <c r="BF8" s="260"/>
+      <c r="BG8" s="260"/>
+      <c r="BH8" s="260"/>
+      <c r="BI8" s="260"/>
+      <c r="BJ8" s="260"/>
+      <c r="BK8" s="260"/>
+      <c r="BL8" s="260"/>
+      <c r="BM8" s="260"/>
+      <c r="BN8" s="260"/>
+      <c r="BO8" s="260"/>
+      <c r="BP8" s="260"/>
+      <c r="BQ8" s="261"/>
+      <c r="BR8" s="315" t="s">
         <v>26</v>
       </c>
-      <c r="BS8" s="275"/>
-      <c r="BT8" s="265" t="s">
+      <c r="BS8" s="322"/>
+      <c r="BT8" s="271" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="268" t="s">
+      <c r="BU8" s="315" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="250" t="s">
+      <c r="BW8" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="253" t="s">
+      <c r="BX8" s="303" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="254"/>
-      <c r="BZ8" s="254"/>
-      <c r="CA8" s="255"/>
-      <c r="CB8" s="262" t="s">
+      <c r="BY8" s="304"/>
+      <c r="BZ8" s="304"/>
+      <c r="CA8" s="305"/>
+      <c r="CB8" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="242" t="s">
+      <c r="CC8" s="297" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="242" t="s">
+      <c r="CD8" s="297" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="300"/>
-      <c r="B9" s="303"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="246"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="284" t="s">
+      <c r="A9" s="278"/>
+      <c r="B9" s="281"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="257"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="242" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="284" t="s">
+      <c r="L9" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="284" t="s">
+      <c r="M9" s="242" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="N9" s="242" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="284" t="s">
+      <c r="O9" s="242" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="284" t="s">
+      <c r="P9" s="242" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="284" t="s">
+      <c r="Q9" s="242" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="284" t="s">
+      <c r="R9" s="242" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="284" t="s">
+      <c r="S9" s="242" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="284" t="s">
+      <c r="T9" s="242" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="284" t="s">
+      <c r="U9" s="242" t="s">
         <v>44</v>
       </c>
       <c r="V9" s="293" t="s">
         <v>45</v>
       </c>
       <c r="W9" s="294"/>
-      <c r="X9" s="284" t="s">
+      <c r="X9" s="242" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="287" t="s">
+      <c r="Y9" s="266" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="287" t="s">
+      <c r="Z9" s="266" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="287" t="s">
+      <c r="AA9" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="287" t="s">
+      <c r="AB9" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="290" t="s">
+      <c r="AC9" s="250" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="290" t="s">
+      <c r="AD9" s="250" t="s">
         <v>52</v>
       </c>
-      <c r="AE9" s="290" t="s">
+      <c r="AE9" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="290" t="s">
+      <c r="AF9" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="287" t="s">
+      <c r="AG9" s="266" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="290" t="s">
+      <c r="AH9" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="290" t="s">
+      <c r="AI9" s="250" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="287" t="s">
+      <c r="AJ9" s="266" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="320" t="s">
+      <c r="AK9" s="247" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="245" t="s">
+      <c r="AL9" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="287" t="s">
+      <c r="AM9" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="317" t="s">
+      <c r="AN9" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="245" t="s">
+      <c r="AO9" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="309"/>
-      <c r="AQ9" s="309"/>
-      <c r="AR9" s="309"/>
-      <c r="AS9" s="309"/>
-      <c r="AT9" s="309"/>
-      <c r="AU9" s="309"/>
-      <c r="AV9" s="246"/>
-      <c r="AW9" s="246"/>
-      <c r="AX9" s="246"/>
-      <c r="AY9" s="313" t="s">
+      <c r="AP9" s="254"/>
+      <c r="AQ9" s="254"/>
+      <c r="AR9" s="254"/>
+      <c r="AS9" s="254"/>
+      <c r="AT9" s="254"/>
+      <c r="AU9" s="254"/>
+      <c r="AV9" s="257"/>
+      <c r="AW9" s="257"/>
+      <c r="AX9" s="257"/>
+      <c r="AY9" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="314"/>
-      <c r="BA9" s="314"/>
-      <c r="BB9" s="314"/>
-      <c r="BC9" s="314"/>
-      <c r="BD9" s="314"/>
-      <c r="BE9" s="314"/>
-      <c r="BF9" s="314"/>
-      <c r="BG9" s="314"/>
-      <c r="BH9" s="314"/>
-      <c r="BI9" s="314"/>
-      <c r="BJ9" s="314"/>
-      <c r="BK9" s="314"/>
-      <c r="BL9" s="315"/>
-      <c r="BM9" s="313" t="s">
+      <c r="AZ9" s="260"/>
+      <c r="BA9" s="260"/>
+      <c r="BB9" s="260"/>
+      <c r="BC9" s="260"/>
+      <c r="BD9" s="260"/>
+      <c r="BE9" s="260"/>
+      <c r="BF9" s="260"/>
+      <c r="BG9" s="260"/>
+      <c r="BH9" s="260"/>
+      <c r="BI9" s="260"/>
+      <c r="BJ9" s="260"/>
+      <c r="BK9" s="260"/>
+      <c r="BL9" s="261"/>
+      <c r="BM9" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="BN9" s="314"/>
-      <c r="BO9" s="314"/>
-      <c r="BP9" s="314"/>
-      <c r="BQ9" s="315"/>
-      <c r="BR9" s="266" t="s">
+      <c r="BN9" s="260"/>
+      <c r="BO9" s="260"/>
+      <c r="BP9" s="260"/>
+      <c r="BQ9" s="261"/>
+      <c r="BR9" s="269" t="s">
         <v>66</v>
       </c>
-      <c r="BS9" s="266" t="s">
+      <c r="BS9" s="269" t="s">
         <v>67</v>
       </c>
-      <c r="BT9" s="266"/>
-      <c r="BU9" s="269"/>
+      <c r="BT9" s="269"/>
+      <c r="BU9" s="316"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="251"/>
-      <c r="BX9" s="256"/>
-      <c r="BY9" s="257"/>
-      <c r="BZ9" s="257"/>
-      <c r="CA9" s="258"/>
-      <c r="CB9" s="263"/>
-      <c r="CC9" s="243"/>
-      <c r="CD9" s="243"/>
+      <c r="BW9" s="301"/>
+      <c r="BX9" s="306"/>
+      <c r="BY9" s="307"/>
+      <c r="BZ9" s="307"/>
+      <c r="CA9" s="308"/>
+      <c r="CB9" s="313"/>
+      <c r="CC9" s="298"/>
+      <c r="CD9" s="298"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="300"/>
-      <c r="B10" s="303"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="246"/>
-      <c r="G10" s="309"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="309"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
-      <c r="R10" s="285"/>
-      <c r="S10" s="285"/>
-      <c r="T10" s="285"/>
-      <c r="U10" s="285"/>
+      <c r="A10" s="278"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="257"/>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="257"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="286"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="243"/>
+      <c r="N10" s="243"/>
+      <c r="O10" s="243"/>
+      <c r="P10" s="243"/>
+      <c r="Q10" s="243"/>
+      <c r="R10" s="243"/>
+      <c r="S10" s="243"/>
+      <c r="T10" s="243"/>
+      <c r="U10" s="243"/>
       <c r="V10" s="295"/>
       <c r="W10" s="296"/>
-      <c r="X10" s="285"/>
-      <c r="Y10" s="288"/>
-      <c r="Z10" s="288"/>
-      <c r="AA10" s="288"/>
-      <c r="AB10" s="288"/>
-      <c r="AC10" s="291"/>
-      <c r="AD10" s="291"/>
-      <c r="AE10" s="291"/>
-      <c r="AF10" s="291"/>
-      <c r="AG10" s="288"/>
-      <c r="AH10" s="291"/>
-      <c r="AI10" s="291"/>
-      <c r="AJ10" s="288"/>
-      <c r="AK10" s="321"/>
-      <c r="AL10" s="246"/>
-      <c r="AM10" s="288"/>
-      <c r="AN10" s="318"/>
-      <c r="AO10" s="246"/>
-      <c r="AP10" s="309"/>
-      <c r="AQ10" s="309"/>
-      <c r="AR10" s="309"/>
-      <c r="AS10" s="309"/>
-      <c r="AT10" s="309"/>
-      <c r="AU10" s="309"/>
-      <c r="AV10" s="246"/>
-      <c r="AW10" s="246"/>
-      <c r="AX10" s="246"/>
+      <c r="X10" s="243"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="267"/>
+      <c r="AA10" s="267"/>
+      <c r="AB10" s="267"/>
+      <c r="AC10" s="251"/>
+      <c r="AD10" s="251"/>
+      <c r="AE10" s="251"/>
+      <c r="AF10" s="251"/>
+      <c r="AG10" s="267"/>
+      <c r="AH10" s="251"/>
+      <c r="AI10" s="251"/>
+      <c r="AJ10" s="267"/>
+      <c r="AK10" s="248"/>
+      <c r="AL10" s="257"/>
+      <c r="AM10" s="267"/>
+      <c r="AN10" s="264"/>
+      <c r="AO10" s="257"/>
+      <c r="AP10" s="254"/>
+      <c r="AQ10" s="254"/>
+      <c r="AR10" s="254"/>
+      <c r="AS10" s="254"/>
+      <c r="AT10" s="254"/>
+      <c r="AU10" s="254"/>
+      <c r="AV10" s="257"/>
+      <c r="AW10" s="257"/>
+      <c r="AX10" s="257"/>
       <c r="AY10" s="101" t="s">
         <v>68</v>
       </c>
@@ -8098,125 +8133,125 @@
       <c r="BA10" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="271" t="s">
+      <c r="BB10" s="318" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="248" t="s">
+      <c r="BC10" s="245" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="248" t="s">
+      <c r="BD10" s="245" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="273" t="s">
+      <c r="BE10" s="320" t="s">
         <v>74</v>
       </c>
-      <c r="BF10" s="248" t="s">
+      <c r="BF10" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="248" t="s">
+      <c r="BG10" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="248" t="s">
+      <c r="BH10" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="248" t="s">
+      <c r="BI10" s="245" t="s">
         <v>78</v>
       </c>
-      <c r="BJ10" s="248" t="s">
+      <c r="BJ10" s="245" t="s">
         <v>79</v>
       </c>
-      <c r="BK10" s="248" t="s">
+      <c r="BK10" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="BL10" s="311" t="s">
+      <c r="BL10" s="283" t="s">
         <v>81</v>
       </c>
-      <c r="BM10" s="248" t="s">
+      <c r="BM10" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="BN10" s="265" t="s">
+      <c r="BN10" s="271" t="s">
         <v>83</v>
       </c>
-      <c r="BO10" s="248" t="s">
+      <c r="BO10" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="BP10" s="265" t="s">
+      <c r="BP10" s="271" t="s">
         <v>85</v>
       </c>
-      <c r="BQ10" s="265" t="s">
+      <c r="BQ10" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="BR10" s="266"/>
-      <c r="BS10" s="266"/>
-      <c r="BT10" s="266"/>
-      <c r="BU10" s="269"/>
+      <c r="BR10" s="269"/>
+      <c r="BS10" s="269"/>
+      <c r="BT10" s="269"/>
+      <c r="BU10" s="316"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="252"/>
-      <c r="BX10" s="259"/>
-      <c r="BY10" s="260"/>
-      <c r="BZ10" s="260"/>
-      <c r="CA10" s="261"/>
-      <c r="CB10" s="264"/>
-      <c r="CC10" s="244"/>
-      <c r="CD10" s="244"/>
+      <c r="BW10" s="302"/>
+      <c r="BX10" s="309"/>
+      <c r="BY10" s="310"/>
+      <c r="BZ10" s="310"/>
+      <c r="CA10" s="311"/>
+      <c r="CB10" s="314"/>
+      <c r="CC10" s="299"/>
+      <c r="CD10" s="299"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="28">
-      <c r="A11" s="301"/>
-      <c r="B11" s="304"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="307"/>
-      <c r="E11" s="307"/>
-      <c r="F11" s="247"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="278"/>
-      <c r="I11" s="278"/>
-      <c r="J11" s="310"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286"/>
-      <c r="T11" s="286"/>
-      <c r="U11" s="286"/>
+      <c r="A11" s="279"/>
+      <c r="B11" s="282"/>
+      <c r="C11" s="258"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="258"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="287"/>
+      <c r="I11" s="287"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
+      <c r="M11" s="244"/>
+      <c r="N11" s="244"/>
+      <c r="O11" s="244"/>
+      <c r="P11" s="244"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="244"/>
+      <c r="T11" s="244"/>
+      <c r="U11" s="244"/>
       <c r="V11" s="30" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="286"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="292"/>
-      <c r="AD11" s="292"/>
-      <c r="AE11" s="292"/>
-      <c r="AF11" s="292"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="292"/>
-      <c r="AI11" s="292"/>
-      <c r="AJ11" s="289"/>
-      <c r="AK11" s="322"/>
-      <c r="AL11" s="247"/>
-      <c r="AM11" s="289"/>
-      <c r="AN11" s="319"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="310"/>
-      <c r="AQ11" s="310"/>
-      <c r="AR11" s="310"/>
-      <c r="AS11" s="310"/>
-      <c r="AT11" s="310"/>
-      <c r="AU11" s="310"/>
-      <c r="AV11" s="247"/>
-      <c r="AW11" s="247"/>
-      <c r="AX11" s="247"/>
+      <c r="X11" s="244"/>
+      <c r="Y11" s="268"/>
+      <c r="Z11" s="268"/>
+      <c r="AA11" s="268"/>
+      <c r="AB11" s="268"/>
+      <c r="AC11" s="252"/>
+      <c r="AD11" s="252"/>
+      <c r="AE11" s="252"/>
+      <c r="AF11" s="252"/>
+      <c r="AG11" s="268"/>
+      <c r="AH11" s="252"/>
+      <c r="AI11" s="252"/>
+      <c r="AJ11" s="268"/>
+      <c r="AK11" s="249"/>
+      <c r="AL11" s="258"/>
+      <c r="AM11" s="268"/>
+      <c r="AN11" s="265"/>
+      <c r="AO11" s="258"/>
+      <c r="AP11" s="255"/>
+      <c r="AQ11" s="255"/>
+      <c r="AR11" s="255"/>
+      <c r="AS11" s="255"/>
+      <c r="AT11" s="255"/>
+      <c r="AU11" s="255"/>
+      <c r="AV11" s="258"/>
+      <c r="AW11" s="258"/>
+      <c r="AX11" s="258"/>
       <c r="AY11" s="102" t="s">
         <v>89</v>
       </c>
@@ -8226,28 +8261,28 @@
       <c r="BA11" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="272"/>
-      <c r="BC11" s="249"/>
-      <c r="BD11" s="249"/>
-      <c r="BE11" s="274"/>
-      <c r="BF11" s="249"/>
-      <c r="BG11" s="249"/>
-      <c r="BH11" s="249"/>
-      <c r="BI11" s="249"/>
-      <c r="BJ11" s="249"/>
-      <c r="BK11" s="249"/>
-      <c r="BL11" s="312"/>
-      <c r="BM11" s="249"/>
-      <c r="BN11" s="267"/>
-      <c r="BO11" s="249"/>
-      <c r="BP11" s="267"/>
-      <c r="BQ11" s="267"/>
-      <c r="BR11" s="267"/>
-      <c r="BS11" s="267"/>
-      <c r="BT11" s="267"/>
-      <c r="BU11" s="270"/>
+      <c r="BB11" s="319"/>
+      <c r="BC11" s="246"/>
+      <c r="BD11" s="246"/>
+      <c r="BE11" s="321"/>
+      <c r="BF11" s="246"/>
+      <c r="BG11" s="246"/>
+      <c r="BH11" s="246"/>
+      <c r="BI11" s="246"/>
+      <c r="BJ11" s="246"/>
+      <c r="BK11" s="246"/>
+      <c r="BL11" s="284"/>
+      <c r="BM11" s="246"/>
+      <c r="BN11" s="270"/>
+      <c r="BO11" s="246"/>
+      <c r="BP11" s="270"/>
+      <c r="BQ11" s="270"/>
+      <c r="BR11" s="270"/>
+      <c r="BS11" s="270"/>
+      <c r="BT11" s="270"/>
+      <c r="BU11" s="317"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="252"/>
+      <c r="BW11" s="302"/>
       <c r="BX11" s="72" t="s">
         <v>92</v>
       </c>
@@ -8260,9 +8295,9 @@
       <c r="CA11" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="264"/>
-      <c r="CC11" s="244"/>
-      <c r="CD11" s="244"/>
+      <c r="CB11" s="314"/>
+      <c r="CC11" s="299"/>
+      <c r="CD11" s="299"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -8842,7 +8877,7 @@
       <c r="BK14" s="81"/>
       <c r="BL14" s="81">
         <f t="shared" si="10"/>
-        <v>10629119</v>
+        <v>13677639</v>
       </c>
       <c r="BM14" s="81">
         <f t="shared" si="10"/>
@@ -8872,7 +8907,7 @@
       </c>
       <c r="BU14" s="104">
         <f t="shared" ref="BU14" si="11">SUM(BU15:BU21)</f>
-        <v>131444288.6923077</v>
+        <v>128395768.6923077</v>
       </c>
       <c r="BV14" s="117"/>
       <c r="BW14" s="108"/>
@@ -9066,9 +9101,7 @@
         <f>AV15-BF15+AW15</f>
         <v>60270000</v>
       </c>
-      <c r="BH15" s="85">
-        <v>3</v>
-      </c>
+      <c r="BH15" s="85"/>
       <c r="BI15" s="85">
         <v>6200000</v>
       </c>
@@ -9078,11 +9111,11 @@
       </c>
       <c r="BK15" s="85">
         <f>BG15-BB15-BC15+BD15-BH15*BI15-BJ15</f>
-        <v>25170400</v>
+        <v>43770400</v>
       </c>
       <c r="BL15" s="84">
         <f>IF(E15="TV", BK15*10%, IF(BK15&gt;0, ROUND(IF(BK15&gt;80000000, BK15*28%-6400000, IF(BK15&gt;50000000, BK15*21%-3100000, IF(BK15&gt;30000000, BK15*15%-1500000, IF(BK15&gt;10000000, BK15*10%-500000, BK15*5%)))), 0), 0))</f>
-        <v>2017040</v>
+        <v>5065560</v>
       </c>
       <c r="BM15" s="85"/>
       <c r="BN15" s="85"/>
@@ -9099,7 +9132,7 @@
       </c>
       <c r="BU15" s="105">
         <f>AV15-BB15-BC15+BD15-BE15-BL15-BM15-BN15-BO15-BP15-BQ15-BR15+BS15-BT15</f>
-        <v>32042006.153846148</v>
+        <v>28993486.153846148</v>
       </c>
       <c r="BV15" s="118"/>
       <c r="BW15" s="108">
@@ -9312,7 +9345,7 @@
       </c>
       <c r="BH16" s="85"/>
       <c r="BI16" s="85">
-        <v>6200001</v>
+        <v>6200000</v>
       </c>
       <c r="BJ16" s="85">
         <f t="shared" ref="BJ16:BJ21" si="35">IF(E16="CT",15500000,0)</f>
@@ -9557,7 +9590,7 @@
       </c>
       <c r="BH17" s="85"/>
       <c r="BI17" s="85">
-        <v>6200002</v>
+        <v>6200000</v>
       </c>
       <c r="BJ17" s="85">
         <f t="shared" si="35"/>
@@ -9802,7 +9835,7 @@
       </c>
       <c r="BH18" s="85"/>
       <c r="BI18" s="85">
-        <v>6200003</v>
+        <v>6200000</v>
       </c>
       <c r="BJ18" s="85">
         <f t="shared" si="35"/>
@@ -10047,7 +10080,7 @@
       </c>
       <c r="BH19" s="85"/>
       <c r="BI19" s="85">
-        <v>6200004</v>
+        <v>6200000</v>
       </c>
       <c r="BJ19" s="85">
         <f t="shared" si="35"/>
@@ -10292,7 +10325,7 @@
       </c>
       <c r="BH20" s="85"/>
       <c r="BI20" s="85">
-        <v>6200005</v>
+        <v>6200000</v>
       </c>
       <c r="BJ20" s="85">
         <f t="shared" si="35"/>
@@ -10539,7 +10572,7 @@
       </c>
       <c r="BH21" s="85"/>
       <c r="BI21" s="85">
-        <v>6200006</v>
+        <v>6200000</v>
       </c>
       <c r="BJ21" s="85">
         <f t="shared" si="35"/>
@@ -10790,24 +10823,54 @@
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="Q9:Q11"/>
-    <mergeCell ref="N9:N11"/>
-    <mergeCell ref="O9:O11"/>
-    <mergeCell ref="P9:P11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AS8:AS11"/>
-    <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AR8:AR11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AY8:BQ8"/>
-    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="CD8:CD11"/>
+    <mergeCell ref="AX8:AX11"/>
+    <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="BW8:BW11"/>
+    <mergeCell ref="BX8:CA10"/>
+    <mergeCell ref="CB8:CB11"/>
+    <mergeCell ref="CC8:CC11"/>
+    <mergeCell ref="BT8:BT11"/>
+    <mergeCell ref="BU8:BU11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BR8:BS8"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="L9:L11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="M9:M11"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="AY9:BL9"/>
+    <mergeCell ref="BM9:BQ9"/>
+    <mergeCell ref="K9:K11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BQ10:BQ11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BJ10:BJ11"/>
     <mergeCell ref="AN9:AN11"/>
@@ -10824,54 +10887,24 @@
     <mergeCell ref="BO10:BO11"/>
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="E8:E11"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="AY9:BL9"/>
-    <mergeCell ref="BM9:BQ9"/>
-    <mergeCell ref="K9:K11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BQ10:BQ11"/>
-    <mergeCell ref="BI10:BI11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="L9:L11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AO9:AO11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="M9:M11"/>
-    <mergeCell ref="CD8:CD11"/>
-    <mergeCell ref="AX8:AX11"/>
-    <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BX8:CA10"/>
-    <mergeCell ref="CB8:CB11"/>
-    <mergeCell ref="CC8:CC11"/>
-    <mergeCell ref="BT8:BT11"/>
-    <mergeCell ref="BU8:BU11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BR8:BS8"/>
-    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="AS8:AS11"/>
+    <mergeCell ref="AT8:AT11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AR8:AR11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AY8:BQ8"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="N9:N11"/>
+    <mergeCell ref="O9:O11"/>
+    <mergeCell ref="P9:P11"/>
+    <mergeCell ref="BH10:BH11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 C12:BU12 B15:B1048576">
     <cfRule type="duplicateValues" dxfId="23" priority="36"/>
@@ -11084,91 +11117,91 @@
       <c r="CD2" s="137"/>
     </row>
     <row r="3" spans="1:87" s="139" customFormat="1" outlineLevel="1">
-      <c r="A3" s="333" t="str">
+      <c r="A3" s="323" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
-      <c r="I3" s="333"/>
-      <c r="J3" s="333"/>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333"/>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333"/>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
-      <c r="AG3" s="333"/>
-      <c r="AH3" s="333"/>
-      <c r="AI3" s="333"/>
-      <c r="AJ3" s="333"/>
-      <c r="AK3" s="333"/>
-      <c r="AL3" s="333"/>
-      <c r="AM3" s="333"/>
-      <c r="AN3" s="333"/>
-      <c r="AO3" s="333"/>
-      <c r="AP3" s="333"/>
-      <c r="AQ3" s="333"/>
-      <c r="AR3" s="333"/>
-      <c r="AS3" s="333"/>
-      <c r="AT3" s="333"/>
-      <c r="AU3" s="333"/>
-      <c r="AV3" s="333"/>
-      <c r="AW3" s="333"/>
-      <c r="AX3" s="333"/>
-      <c r="AY3" s="333"/>
-      <c r="AZ3" s="333"/>
-      <c r="BA3" s="333"/>
-      <c r="BB3" s="333"/>
-      <c r="BC3" s="333"/>
-      <c r="BD3" s="333"/>
-      <c r="BE3" s="333"/>
-      <c r="BF3" s="333"/>
-      <c r="BG3" s="333"/>
-      <c r="BH3" s="333"/>
-      <c r="BI3" s="333"/>
-      <c r="BJ3" s="333"/>
-      <c r="BK3" s="333"/>
-      <c r="BL3" s="333"/>
-      <c r="BM3" s="333"/>
-      <c r="BN3" s="333"/>
-      <c r="BO3" s="333"/>
-      <c r="BP3" s="333"/>
-      <c r="BQ3" s="333"/>
-      <c r="BR3" s="333"/>
-      <c r="BS3" s="333"/>
-      <c r="BT3" s="333"/>
-      <c r="BU3" s="333"/>
+      <c r="B3" s="323"/>
+      <c r="C3" s="323"/>
+      <c r="D3" s="323"/>
+      <c r="E3" s="323"/>
+      <c r="F3" s="323"/>
+      <c r="G3" s="323"/>
+      <c r="H3" s="323"/>
+      <c r="I3" s="323"/>
+      <c r="J3" s="323"/>
+      <c r="K3" s="323"/>
+      <c r="L3" s="323"/>
+      <c r="M3" s="323"/>
+      <c r="N3" s="323"/>
+      <c r="O3" s="323"/>
+      <c r="P3" s="323"/>
+      <c r="Q3" s="323"/>
+      <c r="R3" s="323"/>
+      <c r="S3" s="323"/>
+      <c r="T3" s="323"/>
+      <c r="U3" s="323"/>
+      <c r="V3" s="323"/>
+      <c r="W3" s="323"/>
+      <c r="X3" s="323"/>
+      <c r="Y3" s="323"/>
+      <c r="Z3" s="323"/>
+      <c r="AA3" s="323"/>
+      <c r="AB3" s="323"/>
+      <c r="AC3" s="323"/>
+      <c r="AD3" s="323"/>
+      <c r="AE3" s="323"/>
+      <c r="AF3" s="323"/>
+      <c r="AG3" s="323"/>
+      <c r="AH3" s="323"/>
+      <c r="AI3" s="323"/>
+      <c r="AJ3" s="323"/>
+      <c r="AK3" s="323"/>
+      <c r="AL3" s="323"/>
+      <c r="AM3" s="323"/>
+      <c r="AN3" s="323"/>
+      <c r="AO3" s="323"/>
+      <c r="AP3" s="323"/>
+      <c r="AQ3" s="323"/>
+      <c r="AR3" s="323"/>
+      <c r="AS3" s="323"/>
+      <c r="AT3" s="323"/>
+      <c r="AU3" s="323"/>
+      <c r="AV3" s="323"/>
+      <c r="AW3" s="323"/>
+      <c r="AX3" s="323"/>
+      <c r="AY3" s="323"/>
+      <c r="AZ3" s="323"/>
+      <c r="BA3" s="323"/>
+      <c r="BB3" s="323"/>
+      <c r="BC3" s="323"/>
+      <c r="BD3" s="323"/>
+      <c r="BE3" s="323"/>
+      <c r="BF3" s="323"/>
+      <c r="BG3" s="323"/>
+      <c r="BH3" s="323"/>
+      <c r="BI3" s="323"/>
+      <c r="BJ3" s="323"/>
+      <c r="BK3" s="323"/>
+      <c r="BL3" s="323"/>
+      <c r="BM3" s="323"/>
+      <c r="BN3" s="323"/>
+      <c r="BO3" s="323"/>
+      <c r="BP3" s="323"/>
+      <c r="BQ3" s="323"/>
+      <c r="BR3" s="323"/>
+      <c r="BS3" s="323"/>
+      <c r="BT3" s="323"/>
+      <c r="BU3" s="323"/>
       <c r="BV3"/>
-      <c r="BW3" s="334" t="s">
+      <c r="BW3" s="324" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="334"/>
-      <c r="BY3" s="334"/>
-      <c r="BZ3" s="334"/>
-      <c r="CA3" s="334"/>
-      <c r="CB3" s="333"/>
+      <c r="BX3" s="324"/>
+      <c r="BY3" s="324"/>
+      <c r="BZ3" s="324"/>
+      <c r="CA3" s="324"/>
+      <c r="CB3" s="323"/>
       <c r="CC3" s="138"/>
       <c r="CD3" s="138"/>
       <c r="CE3" s="139" t="s">
@@ -11252,366 +11285,366 @@
       <c r="BT4" s="140"/>
       <c r="BU4" s="140"/>
       <c r="BV4"/>
-      <c r="BW4" s="333"/>
-      <c r="BX4" s="333"/>
-      <c r="BY4" s="333"/>
-      <c r="BZ4" s="333"/>
-      <c r="CA4" s="333"/>
-      <c r="CB4" s="333"/>
+      <c r="BW4" s="323"/>
+      <c r="BX4" s="323"/>
+      <c r="BY4" s="323"/>
+      <c r="BZ4" s="323"/>
+      <c r="CA4" s="323"/>
+      <c r="CB4" s="323"/>
       <c r="CC4" s="138"/>
       <c r="CD4" s="138"/>
     </row>
     <row r="5" spans="1:87" s="141" customFormat="1">
-      <c r="A5" s="299" t="s">
+      <c r="A5" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="302" t="s">
+      <c r="B5" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="305" t="s">
+      <c r="D5" s="272" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="305" t="s">
+      <c r="E5" s="272" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="245" t="s">
+      <c r="F5" s="256" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="245" t="s">
+      <c r="G5" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="323" t="s">
+      <c r="H5" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="323" t="s">
+      <c r="I5" s="325" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="245" t="s">
+      <c r="J5" s="256" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="335" t="s">
+      <c r="K5" s="328" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="336"/>
-      <c r="M5" s="336"/>
-      <c r="N5" s="336"/>
-      <c r="O5" s="336"/>
-      <c r="P5" s="336"/>
-      <c r="Q5" s="336"/>
-      <c r="R5" s="336"/>
-      <c r="S5" s="336"/>
-      <c r="T5" s="336"/>
-      <c r="U5" s="336"/>
-      <c r="V5" s="336"/>
-      <c r="W5" s="336"/>
-      <c r="X5" s="336"/>
-      <c r="Y5" s="337" t="s">
+      <c r="L5" s="329"/>
+      <c r="M5" s="329"/>
+      <c r="N5" s="329"/>
+      <c r="O5" s="329"/>
+      <c r="P5" s="329"/>
+      <c r="Q5" s="329"/>
+      <c r="R5" s="329"/>
+      <c r="S5" s="329"/>
+      <c r="T5" s="329"/>
+      <c r="U5" s="329"/>
+      <c r="V5" s="329"/>
+      <c r="W5" s="329"/>
+      <c r="X5" s="329"/>
+      <c r="Y5" s="330" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="338"/>
-      <c r="AA5" s="338"/>
-      <c r="AB5" s="338"/>
-      <c r="AC5" s="338"/>
-      <c r="AD5" s="338"/>
-      <c r="AE5" s="338"/>
-      <c r="AF5" s="338"/>
-      <c r="AG5" s="338"/>
-      <c r="AH5" s="338"/>
-      <c r="AI5" s="338"/>
-      <c r="AJ5" s="338"/>
-      <c r="AK5" s="338"/>
-      <c r="AL5" s="338"/>
-      <c r="AM5" s="338"/>
-      <c r="AN5" s="338"/>
-      <c r="AO5" s="339"/>
-      <c r="AP5" s="245" t="s">
+      <c r="Z5" s="331"/>
+      <c r="AA5" s="331"/>
+      <c r="AB5" s="331"/>
+      <c r="AC5" s="331"/>
+      <c r="AD5" s="331"/>
+      <c r="AE5" s="331"/>
+      <c r="AF5" s="331"/>
+      <c r="AG5" s="331"/>
+      <c r="AH5" s="331"/>
+      <c r="AI5" s="331"/>
+      <c r="AJ5" s="331"/>
+      <c r="AK5" s="331"/>
+      <c r="AL5" s="331"/>
+      <c r="AM5" s="331"/>
+      <c r="AN5" s="331"/>
+      <c r="AO5" s="332"/>
+      <c r="AP5" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="245" t="s">
+      <c r="AQ5" s="256" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="245" t="s">
+      <c r="AR5" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="245" t="s">
+      <c r="AS5" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="245" t="s">
+      <c r="AT5" s="256" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="245" t="s">
+      <c r="AU5" s="256" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="245" t="s">
+      <c r="AV5" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="245" t="s">
+      <c r="AW5" s="256" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="245" t="s">
+      <c r="AX5" s="256" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="313" t="s">
+      <c r="AY5" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="314"/>
-      <c r="BA5" s="314"/>
-      <c r="BB5" s="314"/>
-      <c r="BC5" s="314"/>
-      <c r="BD5" s="314"/>
-      <c r="BE5" s="314"/>
-      <c r="BF5" s="314"/>
-      <c r="BG5" s="314"/>
-      <c r="BH5" s="314"/>
-      <c r="BI5" s="314"/>
-      <c r="BJ5" s="314"/>
-      <c r="BK5" s="314"/>
-      <c r="BL5" s="314"/>
-      <c r="BM5" s="314"/>
-      <c r="BN5" s="314"/>
-      <c r="BO5" s="314"/>
-      <c r="BP5" s="314"/>
-      <c r="BQ5" s="315"/>
-      <c r="BR5" s="268" t="s">
+      <c r="AZ5" s="260"/>
+      <c r="BA5" s="260"/>
+      <c r="BB5" s="260"/>
+      <c r="BC5" s="260"/>
+      <c r="BD5" s="260"/>
+      <c r="BE5" s="260"/>
+      <c r="BF5" s="260"/>
+      <c r="BG5" s="260"/>
+      <c r="BH5" s="260"/>
+      <c r="BI5" s="260"/>
+      <c r="BJ5" s="260"/>
+      <c r="BK5" s="260"/>
+      <c r="BL5" s="260"/>
+      <c r="BM5" s="260"/>
+      <c r="BN5" s="260"/>
+      <c r="BO5" s="260"/>
+      <c r="BP5" s="260"/>
+      <c r="BQ5" s="261"/>
+      <c r="BR5" s="315" t="s">
         <v>26</v>
       </c>
-      <c r="BS5" s="275"/>
-      <c r="BT5" s="265" t="s">
+      <c r="BS5" s="322"/>
+      <c r="BT5" s="271" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="268" t="s">
+      <c r="BU5" s="315" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="250" t="s">
+      <c r="BW5" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="253" t="s">
+      <c r="BX5" s="303" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="254"/>
-      <c r="BZ5" s="254"/>
-      <c r="CA5" s="255"/>
-      <c r="CB5" s="262" t="s">
+      <c r="BY5" s="304"/>
+      <c r="BZ5" s="304"/>
+      <c r="CA5" s="305"/>
+      <c r="CB5" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="242" t="s">
+      <c r="CC5" s="297" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="242" t="s">
+      <c r="CD5" s="297" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="142"/>
       <c r="CI5" s="143"/>
     </row>
     <row r="6" spans="1:87" s="141" customFormat="1">
-      <c r="A6" s="300"/>
-      <c r="B6" s="303"/>
-      <c r="C6" s="246"/>
-      <c r="D6" s="306"/>
-      <c r="E6" s="306"/>
-      <c r="F6" s="246"/>
-      <c r="G6" s="246"/>
-      <c r="H6" s="324"/>
-      <c r="I6" s="324"/>
-      <c r="J6" s="246"/>
-      <c r="K6" s="326" t="s">
+      <c r="A6" s="278"/>
+      <c r="B6" s="281"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="273"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="257"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="326"/>
+      <c r="I6" s="326"/>
+      <c r="J6" s="257"/>
+      <c r="K6" s="333" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="326" t="s">
+      <c r="L6" s="333" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="326" t="s">
+      <c r="M6" s="333" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="326" t="s">
+      <c r="N6" s="333" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="326" t="s">
+      <c r="O6" s="333" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="326" t="s">
+      <c r="P6" s="333" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="326" t="s">
+      <c r="Q6" s="333" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="326" t="s">
+      <c r="R6" s="333" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="326" t="s">
+      <c r="S6" s="333" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="326" t="s">
+      <c r="T6" s="333" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="326" t="s">
+      <c r="U6" s="333" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="329" t="s">
+      <c r="V6" s="336" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="330"/>
-      <c r="X6" s="326" t="s">
+      <c r="W6" s="337"/>
+      <c r="X6" s="333" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="245" t="s">
+      <c r="Y6" s="256" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="245" t="s">
+      <c r="Z6" s="256" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="245" t="s">
+      <c r="AA6" s="256" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="245" t="s">
+      <c r="AB6" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="323" t="s">
+      <c r="AC6" s="325" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="323" t="s">
+      <c r="AD6" s="325" t="s">
         <v>52</v>
       </c>
-      <c r="AE6" s="323" t="s">
+      <c r="AE6" s="325" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="323" t="s">
+      <c r="AF6" s="325" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="245" t="s">
+      <c r="AG6" s="256" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="323" t="s">
+      <c r="AH6" s="325" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="323" t="s">
+      <c r="AI6" s="325" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="245" t="s">
+      <c r="AJ6" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="320" t="s">
+      <c r="AK6" s="247" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="245" t="s">
+      <c r="AL6" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="245" t="s">
+      <c r="AM6" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="317" t="s">
+      <c r="AN6" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="245" t="s">
+      <c r="AO6" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="246"/>
-      <c r="AQ6" s="246"/>
-      <c r="AR6" s="246"/>
-      <c r="AS6" s="246"/>
-      <c r="AT6" s="246"/>
-      <c r="AU6" s="246"/>
-      <c r="AV6" s="246"/>
-      <c r="AW6" s="246"/>
-      <c r="AX6" s="246"/>
-      <c r="AY6" s="313" t="s">
+      <c r="AP6" s="257"/>
+      <c r="AQ6" s="257"/>
+      <c r="AR6" s="257"/>
+      <c r="AS6" s="257"/>
+      <c r="AT6" s="257"/>
+      <c r="AU6" s="257"/>
+      <c r="AV6" s="257"/>
+      <c r="AW6" s="257"/>
+      <c r="AX6" s="257"/>
+      <c r="AY6" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="314"/>
-      <c r="BA6" s="314"/>
-      <c r="BB6" s="314"/>
-      <c r="BC6" s="314"/>
-      <c r="BD6" s="314"/>
-      <c r="BE6" s="314"/>
-      <c r="BF6" s="314"/>
-      <c r="BG6" s="314"/>
-      <c r="BH6" s="314"/>
-      <c r="BI6" s="314"/>
-      <c r="BJ6" s="314"/>
-      <c r="BK6" s="314"/>
-      <c r="BL6" s="315"/>
-      <c r="BM6" s="313" t="s">
+      <c r="AZ6" s="260"/>
+      <c r="BA6" s="260"/>
+      <c r="BB6" s="260"/>
+      <c r="BC6" s="260"/>
+      <c r="BD6" s="260"/>
+      <c r="BE6" s="260"/>
+      <c r="BF6" s="260"/>
+      <c r="BG6" s="260"/>
+      <c r="BH6" s="260"/>
+      <c r="BI6" s="260"/>
+      <c r="BJ6" s="260"/>
+      <c r="BK6" s="260"/>
+      <c r="BL6" s="261"/>
+      <c r="BM6" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="BN6" s="314"/>
-      <c r="BO6" s="314"/>
-      <c r="BP6" s="314"/>
-      <c r="BQ6" s="315"/>
-      <c r="BR6" s="266" t="s">
+      <c r="BN6" s="260"/>
+      <c r="BO6" s="260"/>
+      <c r="BP6" s="260"/>
+      <c r="BQ6" s="261"/>
+      <c r="BR6" s="269" t="s">
         <v>66</v>
       </c>
-      <c r="BS6" s="266" t="s">
+      <c r="BS6" s="269" t="s">
         <v>67</v>
       </c>
-      <c r="BT6" s="266"/>
-      <c r="BU6" s="269"/>
+      <c r="BT6" s="269"/>
+      <c r="BU6" s="316"/>
       <c r="BV6"/>
-      <c r="BW6" s="251"/>
-      <c r="BX6" s="256"/>
-      <c r="BY6" s="257"/>
-      <c r="BZ6" s="257"/>
-      <c r="CA6" s="258"/>
-      <c r="CB6" s="263"/>
-      <c r="CC6" s="243"/>
-      <c r="CD6" s="243"/>
+      <c r="BW6" s="301"/>
+      <c r="BX6" s="306"/>
+      <c r="BY6" s="307"/>
+      <c r="BZ6" s="307"/>
+      <c r="CA6" s="308"/>
+      <c r="CB6" s="313"/>
+      <c r="CC6" s="298"/>
+      <c r="CD6" s="298"/>
       <c r="CH6" s="142"/>
       <c r="CI6" s="143"/>
     </row>
     <row r="7" spans="1:87" s="144" customFormat="1">
-      <c r="A7" s="300"/>
-      <c r="B7" s="303"/>
-      <c r="C7" s="246"/>
-      <c r="D7" s="306"/>
-      <c r="E7" s="306"/>
-      <c r="F7" s="246"/>
-      <c r="G7" s="246"/>
-      <c r="H7" s="324"/>
-      <c r="I7" s="324"/>
-      <c r="J7" s="246"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
-      <c r="O7" s="327"/>
-      <c r="P7" s="327"/>
-      <c r="Q7" s="327"/>
-      <c r="R7" s="327"/>
-      <c r="S7" s="327"/>
-      <c r="T7" s="327"/>
-      <c r="U7" s="327"/>
-      <c r="V7" s="331"/>
-      <c r="W7" s="332"/>
-      <c r="X7" s="327"/>
-      <c r="Y7" s="246"/>
-      <c r="Z7" s="246"/>
-      <c r="AA7" s="246"/>
-      <c r="AB7" s="246"/>
-      <c r="AC7" s="324"/>
-      <c r="AD7" s="324"/>
-      <c r="AE7" s="324"/>
-      <c r="AF7" s="324"/>
-      <c r="AG7" s="246"/>
-      <c r="AH7" s="324"/>
-      <c r="AI7" s="324"/>
-      <c r="AJ7" s="246"/>
-      <c r="AK7" s="321"/>
-      <c r="AL7" s="246"/>
-      <c r="AM7" s="246"/>
-      <c r="AN7" s="318"/>
-      <c r="AO7" s="246"/>
-      <c r="AP7" s="246"/>
-      <c r="AQ7" s="246"/>
-      <c r="AR7" s="246"/>
-      <c r="AS7" s="246"/>
-      <c r="AT7" s="246"/>
-      <c r="AU7" s="246"/>
-      <c r="AV7" s="246"/>
-      <c r="AW7" s="246"/>
-      <c r="AX7" s="246"/>
+      <c r="A7" s="278"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="257"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="326"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="257"/>
+      <c r="K7" s="334"/>
+      <c r="L7" s="334"/>
+      <c r="M7" s="334"/>
+      <c r="N7" s="334"/>
+      <c r="O7" s="334"/>
+      <c r="P7" s="334"/>
+      <c r="Q7" s="334"/>
+      <c r="R7" s="334"/>
+      <c r="S7" s="334"/>
+      <c r="T7" s="334"/>
+      <c r="U7" s="334"/>
+      <c r="V7" s="338"/>
+      <c r="W7" s="339"/>
+      <c r="X7" s="334"/>
+      <c r="Y7" s="257"/>
+      <c r="Z7" s="257"/>
+      <c r="AA7" s="257"/>
+      <c r="AB7" s="257"/>
+      <c r="AC7" s="326"/>
+      <c r="AD7" s="326"/>
+      <c r="AE7" s="326"/>
+      <c r="AF7" s="326"/>
+      <c r="AG7" s="257"/>
+      <c r="AH7" s="326"/>
+      <c r="AI7" s="326"/>
+      <c r="AJ7" s="257"/>
+      <c r="AK7" s="248"/>
+      <c r="AL7" s="257"/>
+      <c r="AM7" s="257"/>
+      <c r="AN7" s="264"/>
+      <c r="AO7" s="257"/>
+      <c r="AP7" s="257"/>
+      <c r="AQ7" s="257"/>
+      <c r="AR7" s="257"/>
+      <c r="AS7" s="257"/>
+      <c r="AT7" s="257"/>
+      <c r="AU7" s="257"/>
+      <c r="AV7" s="257"/>
+      <c r="AW7" s="257"/>
+      <c r="AX7" s="257"/>
       <c r="AY7" s="101" t="s">
         <v>68</v>
       </c>
@@ -11621,125 +11654,125 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="265" t="s">
+      <c r="BB7" s="271" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="248" t="s">
+      <c r="BC7" s="245" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="248" t="s">
+      <c r="BD7" s="245" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="273" t="s">
+      <c r="BE7" s="320" t="s">
         <v>74</v>
       </c>
-      <c r="BF7" s="248" t="s">
+      <c r="BF7" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="248" t="s">
+      <c r="BG7" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="248" t="s">
+      <c r="BH7" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="248" t="s">
+      <c r="BI7" s="245" t="s">
         <v>78</v>
       </c>
-      <c r="BJ7" s="248" t="s">
+      <c r="BJ7" s="245" t="s">
         <v>79</v>
       </c>
-      <c r="BK7" s="248" t="s">
+      <c r="BK7" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="BL7" s="311" t="s">
+      <c r="BL7" s="283" t="s">
         <v>81</v>
       </c>
-      <c r="BM7" s="248" t="s">
+      <c r="BM7" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="BN7" s="265" t="s">
+      <c r="BN7" s="271" t="s">
         <v>83</v>
       </c>
-      <c r="BO7" s="248" t="s">
+      <c r="BO7" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="BP7" s="265" t="s">
+      <c r="BP7" s="271" t="s">
         <v>85</v>
       </c>
-      <c r="BQ7" s="265" t="s">
+      <c r="BQ7" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="BR7" s="266"/>
-      <c r="BS7" s="266"/>
-      <c r="BT7" s="266"/>
-      <c r="BU7" s="269"/>
+      <c r="BR7" s="269"/>
+      <c r="BS7" s="269"/>
+      <c r="BT7" s="269"/>
+      <c r="BU7" s="316"/>
       <c r="BV7"/>
-      <c r="BW7" s="252"/>
-      <c r="BX7" s="259"/>
-      <c r="BY7" s="260"/>
-      <c r="BZ7" s="260"/>
-      <c r="CA7" s="261"/>
-      <c r="CB7" s="264"/>
-      <c r="CC7" s="244"/>
-      <c r="CD7" s="244"/>
+      <c r="BW7" s="302"/>
+      <c r="BX7" s="309"/>
+      <c r="BY7" s="310"/>
+      <c r="BZ7" s="310"/>
+      <c r="CA7" s="311"/>
+      <c r="CB7" s="314"/>
+      <c r="CC7" s="299"/>
+      <c r="CD7" s="299"/>
       <c r="CH7" s="142"/>
       <c r="CI7" s="143"/>
     </row>
     <row r="8" spans="1:87" s="144" customFormat="1">
-      <c r="A8" s="301"/>
-      <c r="B8" s="304"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
-      <c r="F8" s="247"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="325"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="328"/>
-      <c r="L8" s="328"/>
-      <c r="M8" s="328"/>
-      <c r="N8" s="328"/>
-      <c r="O8" s="328"/>
-      <c r="P8" s="328"/>
-      <c r="Q8" s="328"/>
-      <c r="R8" s="328"/>
-      <c r="S8" s="328"/>
-      <c r="T8" s="328"/>
-      <c r="U8" s="328"/>
+      <c r="A8" s="279"/>
+      <c r="B8" s="282"/>
+      <c r="C8" s="258"/>
+      <c r="D8" s="274"/>
+      <c r="E8" s="274"/>
+      <c r="F8" s="258"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="327"/>
+      <c r="I8" s="327"/>
+      <c r="J8" s="258"/>
+      <c r="K8" s="335"/>
+      <c r="L8" s="335"/>
+      <c r="M8" s="335"/>
+      <c r="N8" s="335"/>
+      <c r="O8" s="335"/>
+      <c r="P8" s="335"/>
+      <c r="Q8" s="335"/>
+      <c r="R8" s="335"/>
+      <c r="S8" s="335"/>
+      <c r="T8" s="335"/>
+      <c r="U8" s="335"/>
       <c r="V8" s="145" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="328"/>
-      <c r="Y8" s="247"/>
-      <c r="Z8" s="247"/>
-      <c r="AA8" s="247"/>
-      <c r="AB8" s="247"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="247"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="247"/>
-      <c r="AK8" s="322"/>
-      <c r="AL8" s="247"/>
-      <c r="AM8" s="247"/>
-      <c r="AN8" s="319"/>
-      <c r="AO8" s="247"/>
-      <c r="AP8" s="247"/>
-      <c r="AQ8" s="247"/>
-      <c r="AR8" s="247"/>
-      <c r="AS8" s="247"/>
-      <c r="AT8" s="247"/>
-      <c r="AU8" s="247"/>
-      <c r="AV8" s="247"/>
-      <c r="AW8" s="247"/>
-      <c r="AX8" s="247"/>
+      <c r="X8" s="335"/>
+      <c r="Y8" s="258"/>
+      <c r="Z8" s="258"/>
+      <c r="AA8" s="258"/>
+      <c r="AB8" s="258"/>
+      <c r="AC8" s="327"/>
+      <c r="AD8" s="327"/>
+      <c r="AE8" s="327"/>
+      <c r="AF8" s="327"/>
+      <c r="AG8" s="258"/>
+      <c r="AH8" s="327"/>
+      <c r="AI8" s="327"/>
+      <c r="AJ8" s="258"/>
+      <c r="AK8" s="249"/>
+      <c r="AL8" s="258"/>
+      <c r="AM8" s="258"/>
+      <c r="AN8" s="265"/>
+      <c r="AO8" s="258"/>
+      <c r="AP8" s="258"/>
+      <c r="AQ8" s="258"/>
+      <c r="AR8" s="258"/>
+      <c r="AS8" s="258"/>
+      <c r="AT8" s="258"/>
+      <c r="AU8" s="258"/>
+      <c r="AV8" s="258"/>
+      <c r="AW8" s="258"/>
+      <c r="AX8" s="258"/>
       <c r="AY8" s="102" t="s">
         <v>89</v>
       </c>
@@ -11749,28 +11782,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="267"/>
-      <c r="BC8" s="249"/>
-      <c r="BD8" s="249"/>
-      <c r="BE8" s="274"/>
-      <c r="BF8" s="249"/>
-      <c r="BG8" s="249"/>
-      <c r="BH8" s="249"/>
-      <c r="BI8" s="249"/>
-      <c r="BJ8" s="249"/>
-      <c r="BK8" s="249"/>
-      <c r="BL8" s="312"/>
-      <c r="BM8" s="249"/>
-      <c r="BN8" s="267"/>
-      <c r="BO8" s="249"/>
-      <c r="BP8" s="267"/>
-      <c r="BQ8" s="267"/>
-      <c r="BR8" s="267"/>
-      <c r="BS8" s="267"/>
-      <c r="BT8" s="267"/>
-      <c r="BU8" s="270"/>
+      <c r="BB8" s="270"/>
+      <c r="BC8" s="246"/>
+      <c r="BD8" s="246"/>
+      <c r="BE8" s="321"/>
+      <c r="BF8" s="246"/>
+      <c r="BG8" s="246"/>
+      <c r="BH8" s="246"/>
+      <c r="BI8" s="246"/>
+      <c r="BJ8" s="246"/>
+      <c r="BK8" s="246"/>
+      <c r="BL8" s="284"/>
+      <c r="BM8" s="246"/>
+      <c r="BN8" s="270"/>
+      <c r="BO8" s="246"/>
+      <c r="BP8" s="270"/>
+      <c r="BQ8" s="270"/>
+      <c r="BR8" s="270"/>
+      <c r="BS8" s="270"/>
+      <c r="BT8" s="270"/>
+      <c r="BU8" s="317"/>
       <c r="BV8"/>
-      <c r="BW8" s="252"/>
+      <c r="BW8" s="302"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -11783,9 +11816,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="264"/>
-      <c r="CC8" s="244"/>
-      <c r="CD8" s="244"/>
+      <c r="CB8" s="314"/>
+      <c r="CC8" s="299"/>
+      <c r="CD8" s="299"/>
       <c r="CE8" s="141"/>
       <c r="CF8" s="146"/>
       <c r="CH8" s="142"/>
@@ -14409,6 +14442,72 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BL6"/>
+    <mergeCell ref="BM6:BQ6"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BQ7:BQ8"/>
+    <mergeCell ref="BJ7:BJ8"/>
+    <mergeCell ref="BK7:BK8"/>
+    <mergeCell ref="BL7:BL8"/>
+    <mergeCell ref="BM7:BM8"/>
+    <mergeCell ref="BN7:BN8"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="BX5:CA7"/>
+    <mergeCell ref="CB5:CB8"/>
+    <mergeCell ref="CC5:CC8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AY5:BQ5"/>
+    <mergeCell ref="BR5:BS5"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BF7:BF8"/>
+    <mergeCell ref="BG7:BG8"/>
+    <mergeCell ref="BH7:BH8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BS6:BS8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AR5:AR8"/>
+    <mergeCell ref="AS5:AS8"/>
+    <mergeCell ref="AT5:AT8"/>
+    <mergeCell ref="AU5:AU8"/>
+    <mergeCell ref="AV5:AV8"/>
+    <mergeCell ref="AW5:AW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
     <mergeCell ref="A3:BU3"/>
     <mergeCell ref="BW3:CB4"/>
     <mergeCell ref="A5:A8"/>
@@ -14425,84 +14524,18 @@
     <mergeCell ref="Y5:AO5"/>
     <mergeCell ref="AP5:AP8"/>
     <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="P6:P8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AR5:AR8"/>
-    <mergeCell ref="AS5:AS8"/>
-    <mergeCell ref="AT5:AT8"/>
-    <mergeCell ref="AU5:AU8"/>
-    <mergeCell ref="AV5:AV8"/>
-    <mergeCell ref="AW5:AW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="AY5:BQ5"/>
-    <mergeCell ref="BR5:BS5"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BF7:BF8"/>
-    <mergeCell ref="BG7:BG8"/>
-    <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BS6:BS8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="BX5:CA7"/>
-    <mergeCell ref="CB5:CB8"/>
-    <mergeCell ref="CC5:CC8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="Y6:Y8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BL6"/>
-    <mergeCell ref="BM6:BQ6"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BQ7:BQ8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BK7:BK8"/>
-    <mergeCell ref="BL7:BL8"/>
-    <mergeCell ref="BM7:BM8"/>
-    <mergeCell ref="BN7:BN8"/>
-    <mergeCell ref="BO7:BO8"/>
   </mergeCells>
   <conditionalFormatting sqref="B12:B16 B1:B9 C9:BU9 B20:B1048576">
-    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B12:B16 B1:B9 D10:F10 J10:BK10 BM10:BU10 C9:BU9 B20:B1048576 BW9:CD10">
     <cfRule type="duplicateValues" dxfId="17" priority="54"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B19:C19">
     <cfRule type="duplicateValues" dxfId="16" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BL10">
     <cfRule type="duplicateValues" dxfId="13" priority="4"/>
@@ -14720,91 +14753,91 @@
       <c r="CD2" s="12"/>
     </row>
     <row r="3" spans="1:87" s="16" customFormat="1" ht="24" customHeight="1" outlineLevel="1">
-      <c r="A3" s="316" t="str">
+      <c r="A3" s="262" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="316"/>
-      <c r="C3" s="316"/>
-      <c r="D3" s="316"/>
-      <c r="E3" s="316"/>
-      <c r="F3" s="316"/>
-      <c r="G3" s="316"/>
-      <c r="H3" s="316"/>
-      <c r="I3" s="316"/>
-      <c r="J3" s="316"/>
-      <c r="K3" s="316"/>
-      <c r="L3" s="316"/>
-      <c r="M3" s="316"/>
-      <c r="N3" s="316"/>
-      <c r="O3" s="316"/>
-      <c r="P3" s="316"/>
-      <c r="Q3" s="316"/>
-      <c r="R3" s="316"/>
-      <c r="S3" s="316"/>
-      <c r="T3" s="316"/>
-      <c r="U3" s="316"/>
-      <c r="V3" s="316"/>
-      <c r="W3" s="316"/>
-      <c r="X3" s="316"/>
-      <c r="Y3" s="316"/>
-      <c r="Z3" s="316"/>
-      <c r="AA3" s="316"/>
-      <c r="AB3" s="316"/>
-      <c r="AC3" s="316"/>
-      <c r="AD3" s="316"/>
-      <c r="AE3" s="316"/>
-      <c r="AF3" s="316"/>
-      <c r="AG3" s="316"/>
-      <c r="AH3" s="316"/>
-      <c r="AI3" s="316"/>
-      <c r="AJ3" s="316"/>
-      <c r="AK3" s="316"/>
-      <c r="AL3" s="316"/>
-      <c r="AM3" s="316"/>
-      <c r="AN3" s="316"/>
-      <c r="AO3" s="316"/>
-      <c r="AP3" s="316"/>
-      <c r="AQ3" s="316"/>
-      <c r="AR3" s="316"/>
-      <c r="AS3" s="316"/>
-      <c r="AT3" s="316"/>
-      <c r="AU3" s="316"/>
-      <c r="AV3" s="316"/>
-      <c r="AW3" s="316"/>
-      <c r="AX3" s="316"/>
-      <c r="AY3" s="316"/>
-      <c r="AZ3" s="316"/>
-      <c r="BA3" s="316"/>
-      <c r="BB3" s="316"/>
-      <c r="BC3" s="316"/>
-      <c r="BD3" s="316"/>
-      <c r="BE3" s="316"/>
-      <c r="BF3" s="316"/>
-      <c r="BG3" s="316"/>
-      <c r="BH3" s="316"/>
-      <c r="BI3" s="316"/>
-      <c r="BJ3" s="316"/>
-      <c r="BK3" s="316"/>
-      <c r="BL3" s="316"/>
-      <c r="BM3" s="316"/>
-      <c r="BN3" s="316"/>
-      <c r="BO3" s="316"/>
-      <c r="BP3" s="316"/>
-      <c r="BQ3" s="316"/>
-      <c r="BR3" s="316"/>
-      <c r="BS3" s="316"/>
-      <c r="BT3" s="316"/>
-      <c r="BU3" s="316"/>
+      <c r="B3" s="262"/>
+      <c r="C3" s="262"/>
+      <c r="D3" s="262"/>
+      <c r="E3" s="262"/>
+      <c r="F3" s="262"/>
+      <c r="G3" s="262"/>
+      <c r="H3" s="262"/>
+      <c r="I3" s="262"/>
+      <c r="J3" s="262"/>
+      <c r="K3" s="262"/>
+      <c r="L3" s="262"/>
+      <c r="M3" s="262"/>
+      <c r="N3" s="262"/>
+      <c r="O3" s="262"/>
+      <c r="P3" s="262"/>
+      <c r="Q3" s="262"/>
+      <c r="R3" s="262"/>
+      <c r="S3" s="262"/>
+      <c r="T3" s="262"/>
+      <c r="U3" s="262"/>
+      <c r="V3" s="262"/>
+      <c r="W3" s="262"/>
+      <c r="X3" s="262"/>
+      <c r="Y3" s="262"/>
+      <c r="Z3" s="262"/>
+      <c r="AA3" s="262"/>
+      <c r="AB3" s="262"/>
+      <c r="AC3" s="262"/>
+      <c r="AD3" s="262"/>
+      <c r="AE3" s="262"/>
+      <c r="AF3" s="262"/>
+      <c r="AG3" s="262"/>
+      <c r="AH3" s="262"/>
+      <c r="AI3" s="262"/>
+      <c r="AJ3" s="262"/>
+      <c r="AK3" s="262"/>
+      <c r="AL3" s="262"/>
+      <c r="AM3" s="262"/>
+      <c r="AN3" s="262"/>
+      <c r="AO3" s="262"/>
+      <c r="AP3" s="262"/>
+      <c r="AQ3" s="262"/>
+      <c r="AR3" s="262"/>
+      <c r="AS3" s="262"/>
+      <c r="AT3" s="262"/>
+      <c r="AU3" s="262"/>
+      <c r="AV3" s="262"/>
+      <c r="AW3" s="262"/>
+      <c r="AX3" s="262"/>
+      <c r="AY3" s="262"/>
+      <c r="AZ3" s="262"/>
+      <c r="BA3" s="262"/>
+      <c r="BB3" s="262"/>
+      <c r="BC3" s="262"/>
+      <c r="BD3" s="262"/>
+      <c r="BE3" s="262"/>
+      <c r="BF3" s="262"/>
+      <c r="BG3" s="262"/>
+      <c r="BH3" s="262"/>
+      <c r="BI3" s="262"/>
+      <c r="BJ3" s="262"/>
+      <c r="BK3" s="262"/>
+      <c r="BL3" s="262"/>
+      <c r="BM3" s="262"/>
+      <c r="BN3" s="262"/>
+      <c r="BO3" s="262"/>
+      <c r="BP3" s="262"/>
+      <c r="BQ3" s="262"/>
+      <c r="BR3" s="262"/>
+      <c r="BS3" s="262"/>
+      <c r="BT3" s="262"/>
+      <c r="BU3" s="262"/>
       <c r="BV3" s="110"/>
-      <c r="BW3" s="297" t="s">
+      <c r="BW3" s="275" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="297"/>
-      <c r="BY3" s="297"/>
-      <c r="BZ3" s="297"/>
-      <c r="CA3" s="297"/>
-      <c r="CB3" s="298"/>
+      <c r="BX3" s="275"/>
+      <c r="BY3" s="275"/>
+      <c r="BZ3" s="275"/>
+      <c r="CA3" s="275"/>
+      <c r="CB3" s="276"/>
       <c r="CC3" s="71"/>
       <c r="CD3" s="71"/>
       <c r="CE3" s="16" t="s">
@@ -14888,12 +14921,12 @@
       <c r="BT4" s="15"/>
       <c r="BU4" s="15"/>
       <c r="BV4" s="111"/>
-      <c r="BW4" s="298"/>
-      <c r="BX4" s="298"/>
-      <c r="BY4" s="298"/>
-      <c r="BZ4" s="298"/>
-      <c r="CA4" s="298"/>
-      <c r="CB4" s="298"/>
+      <c r="BW4" s="276"/>
+      <c r="BX4" s="276"/>
+      <c r="BY4" s="276"/>
+      <c r="BZ4" s="276"/>
+      <c r="CA4" s="276"/>
+      <c r="CB4" s="276"/>
       <c r="CC4" s="71"/>
       <c r="CD4" s="71"/>
     </row>
@@ -14971,12 +15004,12 @@
       <c r="BT5" s="15"/>
       <c r="BU5" s="15"/>
       <c r="BV5" s="111"/>
-      <c r="BW5" s="298"/>
-      <c r="BX5" s="298"/>
-      <c r="BY5" s="298"/>
-      <c r="BZ5" s="298"/>
-      <c r="CA5" s="298"/>
-      <c r="CB5" s="298"/>
+      <c r="BW5" s="276"/>
+      <c r="BX5" s="276"/>
+      <c r="BY5" s="276"/>
+      <c r="BZ5" s="276"/>
+      <c r="CA5" s="276"/>
+      <c r="CB5" s="276"/>
       <c r="CC5" s="71"/>
       <c r="CD5" s="71"/>
     </row>
@@ -15054,12 +15087,12 @@
       <c r="BT6" s="18"/>
       <c r="BU6" s="18"/>
       <c r="BV6" s="112"/>
-      <c r="BW6" s="297"/>
-      <c r="BX6" s="297"/>
-      <c r="BY6" s="297"/>
-      <c r="BZ6" s="297"/>
-      <c r="CA6" s="297"/>
-      <c r="CB6" s="298"/>
+      <c r="BW6" s="275"/>
+      <c r="BX6" s="275"/>
+      <c r="BY6" s="275"/>
+      <c r="BZ6" s="275"/>
+      <c r="CA6" s="275"/>
+      <c r="CB6" s="276"/>
       <c r="CC6" s="71"/>
       <c r="CD6" s="71"/>
     </row>
@@ -15147,358 +15180,358 @@
       <c r="CD7" s="25"/>
     </row>
     <row r="8" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A8" s="299" t="s">
+      <c r="A8" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="302" t="s">
+      <c r="B8" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="245" t="s">
+      <c r="C8" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="305" t="s">
+      <c r="D8" s="272" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="305" t="s">
+      <c r="E8" s="272" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="340" t="s">
+      <c r="F8" s="348" t="s">
         <v>127</v>
       </c>
-      <c r="G8" s="308" t="s">
+      <c r="G8" s="253" t="s">
         <v>10</v>
       </c>
-      <c r="H8" s="276" t="s">
+      <c r="H8" s="285" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="276" t="s">
+      <c r="I8" s="285" t="s">
         <v>12</v>
       </c>
-      <c r="J8" s="308" t="s">
+      <c r="J8" s="253" t="s">
         <v>13</v>
       </c>
-      <c r="K8" s="279" t="s">
+      <c r="K8" s="288" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="280"/>
-      <c r="M8" s="280"/>
-      <c r="N8" s="280"/>
-      <c r="O8" s="280"/>
-      <c r="P8" s="280"/>
-      <c r="Q8" s="280"/>
-      <c r="R8" s="280"/>
-      <c r="S8" s="280"/>
-      <c r="T8" s="280"/>
-      <c r="U8" s="280"/>
-      <c r="V8" s="280"/>
-      <c r="W8" s="280"/>
-      <c r="X8" s="280"/>
-      <c r="Y8" s="281" t="s">
+      <c r="L8" s="289"/>
+      <c r="M8" s="289"/>
+      <c r="N8" s="289"/>
+      <c r="O8" s="289"/>
+      <c r="P8" s="289"/>
+      <c r="Q8" s="289"/>
+      <c r="R8" s="289"/>
+      <c r="S8" s="289"/>
+      <c r="T8" s="289"/>
+      <c r="U8" s="289"/>
+      <c r="V8" s="289"/>
+      <c r="W8" s="289"/>
+      <c r="X8" s="289"/>
+      <c r="Y8" s="290" t="s">
         <v>15</v>
       </c>
-      <c r="Z8" s="282"/>
-      <c r="AA8" s="282"/>
-      <c r="AB8" s="282"/>
-      <c r="AC8" s="282"/>
-      <c r="AD8" s="282"/>
-      <c r="AE8" s="282"/>
-      <c r="AF8" s="282"/>
-      <c r="AG8" s="282"/>
-      <c r="AH8" s="282"/>
-      <c r="AI8" s="282"/>
-      <c r="AJ8" s="282"/>
-      <c r="AK8" s="282"/>
-      <c r="AL8" s="282"/>
-      <c r="AM8" s="282"/>
-      <c r="AN8" s="282"/>
-      <c r="AO8" s="283"/>
-      <c r="AP8" s="308" t="s">
+      <c r="Z8" s="291"/>
+      <c r="AA8" s="291"/>
+      <c r="AB8" s="291"/>
+      <c r="AC8" s="291"/>
+      <c r="AD8" s="291"/>
+      <c r="AE8" s="291"/>
+      <c r="AF8" s="291"/>
+      <c r="AG8" s="291"/>
+      <c r="AH8" s="291"/>
+      <c r="AI8" s="291"/>
+      <c r="AJ8" s="291"/>
+      <c r="AK8" s="291"/>
+      <c r="AL8" s="291"/>
+      <c r="AM8" s="291"/>
+      <c r="AN8" s="291"/>
+      <c r="AO8" s="292"/>
+      <c r="AP8" s="253" t="s">
         <v>16</v>
       </c>
-      <c r="AQ8" s="308" t="s">
+      <c r="AQ8" s="253" t="s">
         <v>17</v>
       </c>
-      <c r="AR8" s="308" t="s">
+      <c r="AR8" s="253" t="s">
         <v>18</v>
       </c>
-      <c r="AS8" s="308" t="s">
+      <c r="AS8" s="253" t="s">
         <v>19</v>
       </c>
-      <c r="AT8" s="308" t="s">
+      <c r="AT8" s="253" t="s">
         <v>20</v>
       </c>
-      <c r="AU8" s="308" t="s">
+      <c r="AU8" s="253" t="s">
         <v>21</v>
       </c>
-      <c r="AV8" s="245" t="s">
+      <c r="AV8" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AW8" s="245" t="s">
+      <c r="AW8" s="256" t="s">
         <v>23</v>
       </c>
-      <c r="AX8" s="245" t="s">
+      <c r="AX8" s="256" t="s">
         <v>24</v>
       </c>
-      <c r="AY8" s="313" t="s">
+      <c r="AY8" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="AZ8" s="314"/>
-      <c r="BA8" s="314"/>
-      <c r="BB8" s="314"/>
-      <c r="BC8" s="314"/>
-      <c r="BD8" s="314"/>
-      <c r="BE8" s="314"/>
-      <c r="BF8" s="314"/>
-      <c r="BG8" s="314"/>
-      <c r="BH8" s="314"/>
-      <c r="BI8" s="314"/>
-      <c r="BJ8" s="314"/>
-      <c r="BK8" s="314"/>
-      <c r="BL8" s="314"/>
-      <c r="BM8" s="314"/>
-      <c r="BN8" s="314"/>
-      <c r="BO8" s="314"/>
-      <c r="BP8" s="315"/>
-      <c r="BQ8" s="268" t="s">
+      <c r="AZ8" s="260"/>
+      <c r="BA8" s="260"/>
+      <c r="BB8" s="260"/>
+      <c r="BC8" s="260"/>
+      <c r="BD8" s="260"/>
+      <c r="BE8" s="260"/>
+      <c r="BF8" s="260"/>
+      <c r="BG8" s="260"/>
+      <c r="BH8" s="260"/>
+      <c r="BI8" s="260"/>
+      <c r="BJ8" s="260"/>
+      <c r="BK8" s="260"/>
+      <c r="BL8" s="260"/>
+      <c r="BM8" s="260"/>
+      <c r="BN8" s="260"/>
+      <c r="BO8" s="260"/>
+      <c r="BP8" s="261"/>
+      <c r="BQ8" s="315" t="s">
         <v>26</v>
       </c>
-      <c r="BR8" s="275"/>
-      <c r="BS8" s="265" t="s">
+      <c r="BR8" s="322"/>
+      <c r="BS8" s="271" t="s">
         <v>128</v>
       </c>
-      <c r="BT8" s="265" t="s">
+      <c r="BT8" s="271" t="s">
         <v>27</v>
       </c>
-      <c r="BU8" s="268" t="s">
+      <c r="BU8" s="315" t="s">
         <v>28</v>
       </c>
       <c r="BV8" s="114"/>
-      <c r="BW8" s="250" t="s">
+      <c r="BW8" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="BX8" s="253" t="s">
+      <c r="BX8" s="303" t="s">
         <v>30</v>
       </c>
-      <c r="BY8" s="254"/>
-      <c r="BZ8" s="254"/>
-      <c r="CA8" s="255"/>
-      <c r="CB8" s="262" t="s">
+      <c r="BY8" s="304"/>
+      <c r="BZ8" s="304"/>
+      <c r="CA8" s="305"/>
+      <c r="CB8" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="CC8" s="242" t="s">
+      <c r="CC8" s="297" t="s">
         <v>32</v>
       </c>
-      <c r="CD8" s="242" t="s">
+      <c r="CD8" s="297" t="s">
         <v>33</v>
       </c>
       <c r="CH8" s="27"/>
       <c r="CI8" s="28"/>
     </row>
     <row r="9" spans="1:87" s="11" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A9" s="300"/>
-      <c r="B9" s="303"/>
-      <c r="C9" s="246"/>
-      <c r="D9" s="306"/>
-      <c r="E9" s="306"/>
-      <c r="F9" s="341"/>
-      <c r="G9" s="309"/>
-      <c r="H9" s="277"/>
-      <c r="I9" s="277"/>
-      <c r="J9" s="309"/>
-      <c r="K9" s="284" t="s">
+      <c r="A9" s="278"/>
+      <c r="B9" s="281"/>
+      <c r="C9" s="257"/>
+      <c r="D9" s="273"/>
+      <c r="E9" s="273"/>
+      <c r="F9" s="349"/>
+      <c r="G9" s="254"/>
+      <c r="H9" s="286"/>
+      <c r="I9" s="286"/>
+      <c r="J9" s="254"/>
+      <c r="K9" s="242" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="284" t="s">
+      <c r="L9" s="242" t="s">
         <v>35</v>
       </c>
-      <c r="M9" s="284" t="s">
+      <c r="M9" s="242" t="s">
         <v>36</v>
       </c>
-      <c r="N9" s="284" t="s">
+      <c r="N9" s="242" t="s">
         <v>37</v>
       </c>
-      <c r="O9" s="284" t="s">
+      <c r="O9" s="242" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="284" t="s">
+      <c r="P9" s="242" t="s">
         <v>39</v>
       </c>
-      <c r="Q9" s="284" t="s">
+      <c r="Q9" s="242" t="s">
         <v>40</v>
       </c>
-      <c r="R9" s="284" t="s">
+      <c r="R9" s="242" t="s">
         <v>41</v>
       </c>
-      <c r="S9" s="284" t="s">
+      <c r="S9" s="242" t="s">
         <v>42</v>
       </c>
-      <c r="T9" s="284" t="s">
+      <c r="T9" s="242" t="s">
         <v>43</v>
       </c>
-      <c r="U9" s="284" t="s">
+      <c r="U9" s="242" t="s">
         <v>44</v>
       </c>
       <c r="V9" s="293" t="s">
         <v>45</v>
       </c>
       <c r="W9" s="294"/>
-      <c r="X9" s="284" t="s">
+      <c r="X9" s="242" t="s">
         <v>46</v>
       </c>
-      <c r="Y9" s="287" t="s">
+      <c r="Y9" s="266" t="s">
         <v>47</v>
       </c>
-      <c r="Z9" s="287" t="s">
+      <c r="Z9" s="266" t="s">
         <v>48</v>
       </c>
-      <c r="AA9" s="287" t="s">
+      <c r="AA9" s="266" t="s">
         <v>49</v>
       </c>
-      <c r="AB9" s="287" t="s">
+      <c r="AB9" s="266" t="s">
         <v>50</v>
       </c>
-      <c r="AC9" s="290" t="s">
+      <c r="AC9" s="250" t="s">
         <v>51</v>
       </c>
-      <c r="AD9" s="290" t="s">
+      <c r="AD9" s="250" t="s">
         <v>129</v>
       </c>
-      <c r="AE9" s="290" t="s">
+      <c r="AE9" s="250" t="s">
         <v>53</v>
       </c>
-      <c r="AF9" s="290" t="s">
+      <c r="AF9" s="250" t="s">
         <v>54</v>
       </c>
-      <c r="AG9" s="287" t="s">
+      <c r="AG9" s="266" t="s">
         <v>55</v>
       </c>
-      <c r="AH9" s="290" t="s">
+      <c r="AH9" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="AI9" s="290" t="s">
+      <c r="AI9" s="250" t="s">
         <v>57</v>
       </c>
-      <c r="AJ9" s="287" t="s">
+      <c r="AJ9" s="266" t="s">
         <v>58</v>
       </c>
-      <c r="AK9" s="320" t="s">
+      <c r="AK9" s="247" t="s">
         <v>59</v>
       </c>
-      <c r="AL9" s="245" t="s">
+      <c r="AL9" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="AM9" s="287" t="s">
+      <c r="AM9" s="266" t="s">
         <v>61</v>
       </c>
-      <c r="AN9" s="317" t="s">
+      <c r="AN9" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="AO9" s="245" t="s">
+      <c r="AO9" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="AP9" s="309"/>
-      <c r="AQ9" s="309"/>
-      <c r="AR9" s="309"/>
-      <c r="AS9" s="309"/>
-      <c r="AT9" s="309"/>
-      <c r="AU9" s="309"/>
-      <c r="AV9" s="246"/>
-      <c r="AW9" s="246"/>
-      <c r="AX9" s="246"/>
-      <c r="AY9" s="313" t="s">
+      <c r="AP9" s="254"/>
+      <c r="AQ9" s="254"/>
+      <c r="AR9" s="254"/>
+      <c r="AS9" s="254"/>
+      <c r="AT9" s="254"/>
+      <c r="AU9" s="254"/>
+      <c r="AV9" s="257"/>
+      <c r="AW9" s="257"/>
+      <c r="AX9" s="257"/>
+      <c r="AY9" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="AZ9" s="314"/>
-      <c r="BA9" s="314"/>
-      <c r="BB9" s="314"/>
-      <c r="BC9" s="314"/>
-      <c r="BD9" s="314"/>
-      <c r="BE9" s="314"/>
-      <c r="BF9" s="314"/>
-      <c r="BG9" s="314"/>
-      <c r="BH9" s="314"/>
-      <c r="BI9" s="314"/>
-      <c r="BJ9" s="315"/>
-      <c r="BK9" s="313" t="s">
+      <c r="AZ9" s="260"/>
+      <c r="BA9" s="260"/>
+      <c r="BB9" s="260"/>
+      <c r="BC9" s="260"/>
+      <c r="BD9" s="260"/>
+      <c r="BE9" s="260"/>
+      <c r="BF9" s="260"/>
+      <c r="BG9" s="260"/>
+      <c r="BH9" s="260"/>
+      <c r="BI9" s="260"/>
+      <c r="BJ9" s="261"/>
+      <c r="BK9" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="BL9" s="314"/>
-      <c r="BM9" s="314"/>
-      <c r="BN9" s="314"/>
-      <c r="BO9" s="314"/>
-      <c r="BP9" s="315"/>
-      <c r="BQ9" s="266" t="s">
+      <c r="BL9" s="260"/>
+      <c r="BM9" s="260"/>
+      <c r="BN9" s="260"/>
+      <c r="BO9" s="260"/>
+      <c r="BP9" s="261"/>
+      <c r="BQ9" s="269" t="s">
         <v>66</v>
       </c>
-      <c r="BR9" s="266" t="s">
+      <c r="BR9" s="269" t="s">
         <v>67</v>
       </c>
-      <c r="BS9" s="266"/>
-      <c r="BT9" s="266"/>
-      <c r="BU9" s="269"/>
+      <c r="BS9" s="269"/>
+      <c r="BT9" s="269"/>
+      <c r="BU9" s="316"/>
       <c r="BV9" s="114"/>
-      <c r="BW9" s="251"/>
-      <c r="BX9" s="256"/>
-      <c r="BY9" s="257"/>
-      <c r="BZ9" s="257"/>
-      <c r="CA9" s="258"/>
-      <c r="CB9" s="263"/>
-      <c r="CC9" s="243"/>
-      <c r="CD9" s="243"/>
+      <c r="BW9" s="301"/>
+      <c r="BX9" s="306"/>
+      <c r="BY9" s="307"/>
+      <c r="BZ9" s="307"/>
+      <c r="CA9" s="308"/>
+      <c r="CB9" s="313"/>
+      <c r="CC9" s="298"/>
+      <c r="CD9" s="298"/>
       <c r="CH9" s="27"/>
       <c r="CI9" s="28"/>
     </row>
     <row r="10" spans="1:87" s="29" customFormat="1" ht="19.25" customHeight="1">
-      <c r="A10" s="300"/>
-      <c r="B10" s="303"/>
-      <c r="C10" s="246"/>
-      <c r="D10" s="306"/>
-      <c r="E10" s="306"/>
-      <c r="F10" s="341"/>
-      <c r="G10" s="309"/>
-      <c r="H10" s="277"/>
-      <c r="I10" s="277"/>
-      <c r="J10" s="309"/>
-      <c r="K10" s="285"/>
-      <c r="L10" s="285"/>
-      <c r="M10" s="285"/>
-      <c r="N10" s="285"/>
-      <c r="O10" s="285"/>
-      <c r="P10" s="285"/>
-      <c r="Q10" s="285"/>
-      <c r="R10" s="285"/>
-      <c r="S10" s="285"/>
-      <c r="T10" s="285"/>
-      <c r="U10" s="285"/>
+      <c r="A10" s="278"/>
+      <c r="B10" s="281"/>
+      <c r="C10" s="257"/>
+      <c r="D10" s="273"/>
+      <c r="E10" s="273"/>
+      <c r="F10" s="349"/>
+      <c r="G10" s="254"/>
+      <c r="H10" s="286"/>
+      <c r="I10" s="286"/>
+      <c r="J10" s="254"/>
+      <c r="K10" s="243"/>
+      <c r="L10" s="243"/>
+      <c r="M10" s="243"/>
+      <c r="N10" s="243"/>
+      <c r="O10" s="243"/>
+      <c r="P10" s="243"/>
+      <c r="Q10" s="243"/>
+      <c r="R10" s="243"/>
+      <c r="S10" s="243"/>
+      <c r="T10" s="243"/>
+      <c r="U10" s="243"/>
       <c r="V10" s="295"/>
       <c r="W10" s="296"/>
-      <c r="X10" s="285"/>
-      <c r="Y10" s="288"/>
-      <c r="Z10" s="288"/>
-      <c r="AA10" s="288"/>
-      <c r="AB10" s="288"/>
-      <c r="AC10" s="291"/>
-      <c r="AD10" s="291"/>
-      <c r="AE10" s="291"/>
-      <c r="AF10" s="291"/>
-      <c r="AG10" s="288"/>
-      <c r="AH10" s="291"/>
-      <c r="AI10" s="291"/>
-      <c r="AJ10" s="288"/>
-      <c r="AK10" s="321"/>
-      <c r="AL10" s="246"/>
-      <c r="AM10" s="288"/>
-      <c r="AN10" s="318"/>
-      <c r="AO10" s="246"/>
-      <c r="AP10" s="309"/>
-      <c r="AQ10" s="309"/>
-      <c r="AR10" s="309"/>
-      <c r="AS10" s="309"/>
-      <c r="AT10" s="309"/>
-      <c r="AU10" s="309"/>
-      <c r="AV10" s="246"/>
-      <c r="AW10" s="246"/>
-      <c r="AX10" s="246"/>
+      <c r="X10" s="243"/>
+      <c r="Y10" s="267"/>
+      <c r="Z10" s="267"/>
+      <c r="AA10" s="267"/>
+      <c r="AB10" s="267"/>
+      <c r="AC10" s="251"/>
+      <c r="AD10" s="251"/>
+      <c r="AE10" s="251"/>
+      <c r="AF10" s="251"/>
+      <c r="AG10" s="267"/>
+      <c r="AH10" s="251"/>
+      <c r="AI10" s="251"/>
+      <c r="AJ10" s="267"/>
+      <c r="AK10" s="248"/>
+      <c r="AL10" s="257"/>
+      <c r="AM10" s="267"/>
+      <c r="AN10" s="264"/>
+      <c r="AO10" s="257"/>
+      <c r="AP10" s="254"/>
+      <c r="AQ10" s="254"/>
+      <c r="AR10" s="254"/>
+      <c r="AS10" s="254"/>
+      <c r="AT10" s="254"/>
+      <c r="AU10" s="254"/>
+      <c r="AV10" s="257"/>
+      <c r="AW10" s="257"/>
+      <c r="AX10" s="257"/>
       <c r="AY10" s="101" t="s">
         <v>68</v>
       </c>
@@ -15508,123 +15541,123 @@
       <c r="BA10" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB10" s="349" t="s">
+      <c r="BB10" s="346" t="s">
         <v>71</v>
       </c>
-      <c r="BC10" s="343" t="s">
+      <c r="BC10" s="344" t="s">
         <v>72</v>
       </c>
-      <c r="BD10" s="343" t="s">
+      <c r="BD10" s="344" t="s">
         <v>73</v>
       </c>
-      <c r="BE10" s="343" t="s">
+      <c r="BE10" s="344" t="s">
         <v>130</v>
       </c>
-      <c r="BF10" s="343" t="s">
+      <c r="BF10" s="344" t="s">
         <v>75</v>
       </c>
-      <c r="BG10" s="343" t="s">
+      <c r="BG10" s="344" t="s">
         <v>76</v>
       </c>
-      <c r="BH10" s="343" t="s">
+      <c r="BH10" s="344" t="s">
         <v>77</v>
       </c>
-      <c r="BI10" s="343" t="s">
+      <c r="BI10" s="344" t="s">
         <v>80</v>
       </c>
-      <c r="BJ10" s="347" t="s">
+      <c r="BJ10" s="342" t="s">
         <v>81</v>
       </c>
-      <c r="BK10" s="343" t="s">
+      <c r="BK10" s="344" t="s">
         <v>82</v>
       </c>
-      <c r="BL10" s="345" t="s">
+      <c r="BL10" s="340" t="s">
         <v>83</v>
       </c>
-      <c r="BM10" s="343" t="s">
+      <c r="BM10" s="344" t="s">
         <v>84</v>
       </c>
-      <c r="BN10" s="345" t="s">
+      <c r="BN10" s="340" t="s">
         <v>85</v>
       </c>
-      <c r="BO10" s="345" t="s">
+      <c r="BO10" s="340" t="s">
         <v>131</v>
       </c>
-      <c r="BP10" s="265" t="s">
+      <c r="BP10" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="BQ10" s="266"/>
-      <c r="BR10" s="266"/>
-      <c r="BS10" s="266"/>
-      <c r="BT10" s="266"/>
-      <c r="BU10" s="269"/>
+      <c r="BQ10" s="269"/>
+      <c r="BR10" s="269"/>
+      <c r="BS10" s="269"/>
+      <c r="BT10" s="269"/>
+      <c r="BU10" s="316"/>
       <c r="BV10" s="114"/>
-      <c r="BW10" s="252"/>
-      <c r="BX10" s="259"/>
-      <c r="BY10" s="260"/>
-      <c r="BZ10" s="260"/>
-      <c r="CA10" s="261"/>
-      <c r="CB10" s="264"/>
-      <c r="CC10" s="244"/>
-      <c r="CD10" s="244"/>
+      <c r="BW10" s="302"/>
+      <c r="BX10" s="309"/>
+      <c r="BY10" s="310"/>
+      <c r="BZ10" s="310"/>
+      <c r="CA10" s="311"/>
+      <c r="CB10" s="314"/>
+      <c r="CC10" s="299"/>
+      <c r="CD10" s="299"/>
       <c r="CH10" s="27"/>
       <c r="CI10" s="28"/>
     </row>
     <row r="11" spans="1:87" s="29" customFormat="1" ht="28">
-      <c r="A11" s="301"/>
-      <c r="B11" s="304"/>
-      <c r="C11" s="247"/>
-      <c r="D11" s="307"/>
-      <c r="E11" s="307"/>
-      <c r="F11" s="342"/>
-      <c r="G11" s="310"/>
-      <c r="H11" s="278"/>
-      <c r="I11" s="278"/>
-      <c r="J11" s="310"/>
-      <c r="K11" s="286"/>
-      <c r="L11" s="286"/>
-      <c r="M11" s="286"/>
-      <c r="N11" s="286"/>
-      <c r="O11" s="286"/>
-      <c r="P11" s="286"/>
-      <c r="Q11" s="286"/>
-      <c r="R11" s="286"/>
-      <c r="S11" s="286"/>
-      <c r="T11" s="286"/>
-      <c r="U11" s="286"/>
+      <c r="A11" s="279"/>
+      <c r="B11" s="282"/>
+      <c r="C11" s="258"/>
+      <c r="D11" s="274"/>
+      <c r="E11" s="274"/>
+      <c r="F11" s="350"/>
+      <c r="G11" s="255"/>
+      <c r="H11" s="287"/>
+      <c r="I11" s="287"/>
+      <c r="J11" s="255"/>
+      <c r="K11" s="244"/>
+      <c r="L11" s="244"/>
+      <c r="M11" s="244"/>
+      <c r="N11" s="244"/>
+      <c r="O11" s="244"/>
+      <c r="P11" s="244"/>
+      <c r="Q11" s="244"/>
+      <c r="R11" s="244"/>
+      <c r="S11" s="244"/>
+      <c r="T11" s="244"/>
+      <c r="U11" s="244"/>
       <c r="V11" s="30" t="s">
         <v>87</v>
       </c>
       <c r="W11" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="X11" s="286"/>
-      <c r="Y11" s="289"/>
-      <c r="Z11" s="289"/>
-      <c r="AA11" s="289"/>
-      <c r="AB11" s="289"/>
-      <c r="AC11" s="292"/>
-      <c r="AD11" s="292"/>
-      <c r="AE11" s="292"/>
-      <c r="AF11" s="292"/>
-      <c r="AG11" s="289"/>
-      <c r="AH11" s="292"/>
-      <c r="AI11" s="292"/>
-      <c r="AJ11" s="289"/>
-      <c r="AK11" s="322"/>
-      <c r="AL11" s="247"/>
-      <c r="AM11" s="289"/>
-      <c r="AN11" s="319"/>
-      <c r="AO11" s="247"/>
-      <c r="AP11" s="310"/>
-      <c r="AQ11" s="310"/>
-      <c r="AR11" s="310"/>
-      <c r="AS11" s="310"/>
-      <c r="AT11" s="310"/>
-      <c r="AU11" s="310"/>
-      <c r="AV11" s="247"/>
-      <c r="AW11" s="247"/>
-      <c r="AX11" s="247"/>
+      <c r="X11" s="244"/>
+      <c r="Y11" s="268"/>
+      <c r="Z11" s="268"/>
+      <c r="AA11" s="268"/>
+      <c r="AB11" s="268"/>
+      <c r="AC11" s="252"/>
+      <c r="AD11" s="252"/>
+      <c r="AE11" s="252"/>
+      <c r="AF11" s="252"/>
+      <c r="AG11" s="268"/>
+      <c r="AH11" s="252"/>
+      <c r="AI11" s="252"/>
+      <c r="AJ11" s="268"/>
+      <c r="AK11" s="249"/>
+      <c r="AL11" s="258"/>
+      <c r="AM11" s="268"/>
+      <c r="AN11" s="265"/>
+      <c r="AO11" s="258"/>
+      <c r="AP11" s="255"/>
+      <c r="AQ11" s="255"/>
+      <c r="AR11" s="255"/>
+      <c r="AS11" s="255"/>
+      <c r="AT11" s="255"/>
+      <c r="AU11" s="255"/>
+      <c r="AV11" s="258"/>
+      <c r="AW11" s="258"/>
+      <c r="AX11" s="258"/>
       <c r="AY11" s="102" t="s">
         <v>89</v>
       </c>
@@ -15634,28 +15667,28 @@
       <c r="BA11" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB11" s="350"/>
-      <c r="BC11" s="344"/>
-      <c r="BD11" s="344"/>
-      <c r="BE11" s="344"/>
-      <c r="BF11" s="344"/>
-      <c r="BG11" s="344"/>
-      <c r="BH11" s="344"/>
-      <c r="BI11" s="344"/>
-      <c r="BJ11" s="348"/>
-      <c r="BK11" s="344"/>
-      <c r="BL11" s="346"/>
-      <c r="BM11" s="344"/>
-      <c r="BN11" s="346"/>
-      <c r="BO11" s="346"/>
-      <c r="BP11" s="267"/>
-      <c r="BQ11" s="267"/>
-      <c r="BR11" s="267"/>
-      <c r="BS11" s="267"/>
-      <c r="BT11" s="267"/>
-      <c r="BU11" s="270"/>
+      <c r="BB11" s="347"/>
+      <c r="BC11" s="345"/>
+      <c r="BD11" s="345"/>
+      <c r="BE11" s="345"/>
+      <c r="BF11" s="345"/>
+      <c r="BG11" s="345"/>
+      <c r="BH11" s="345"/>
+      <c r="BI11" s="345"/>
+      <c r="BJ11" s="343"/>
+      <c r="BK11" s="345"/>
+      <c r="BL11" s="341"/>
+      <c r="BM11" s="345"/>
+      <c r="BN11" s="341"/>
+      <c r="BO11" s="341"/>
+      <c r="BP11" s="270"/>
+      <c r="BQ11" s="270"/>
+      <c r="BR11" s="270"/>
+      <c r="BS11" s="270"/>
+      <c r="BT11" s="270"/>
+      <c r="BU11" s="317"/>
       <c r="BV11" s="114"/>
-      <c r="BW11" s="252"/>
+      <c r="BW11" s="302"/>
       <c r="BX11" s="72" t="s">
         <v>92</v>
       </c>
@@ -15668,9 +15701,9 @@
       <c r="CA11" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB11" s="264"/>
-      <c r="CC11" s="244"/>
-      <c r="CD11" s="244"/>
+      <c r="CB11" s="314"/>
+      <c r="CC11" s="299"/>
+      <c r="CD11" s="299"/>
       <c r="CE11" s="11"/>
       <c r="CF11" s="31"/>
       <c r="CH11" s="27"/>
@@ -18069,32 +18102,40 @@
   <autoFilter ref="A12:CI21" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="BS8:BS11"/>
-    <mergeCell ref="BO10:BO11"/>
-    <mergeCell ref="BJ10:BJ11"/>
-    <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="BL10:BL11"/>
-    <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BN10:BN11"/>
-    <mergeCell ref="BP10:BP11"/>
-    <mergeCell ref="AY9:BJ9"/>
-    <mergeCell ref="BK9:BP9"/>
-    <mergeCell ref="BQ9:BQ11"/>
-    <mergeCell ref="BR9:BR11"/>
-    <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="AF9:AF11"/>
-    <mergeCell ref="BC10:BC11"/>
-    <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BE10:BE11"/>
-    <mergeCell ref="AH9:AH11"/>
-    <mergeCell ref="AI9:AI11"/>
-    <mergeCell ref="AJ9:AJ11"/>
-    <mergeCell ref="AK9:AK11"/>
-    <mergeCell ref="AL9:AL11"/>
-    <mergeCell ref="AM9:AM11"/>
-    <mergeCell ref="AQ8:AQ11"/>
-    <mergeCell ref="AN9:AN11"/>
-    <mergeCell ref="AO9:AO11"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB6"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="C8:C11"/>
+    <mergeCell ref="D8:D11"/>
+    <mergeCell ref="E8:E11"/>
+    <mergeCell ref="F8:F11"/>
+    <mergeCell ref="G8:G11"/>
+    <mergeCell ref="H8:H11"/>
+    <mergeCell ref="I8:I11"/>
+    <mergeCell ref="J8:J11"/>
+    <mergeCell ref="K8:X8"/>
+    <mergeCell ref="Y8:AO8"/>
+    <mergeCell ref="AP8:AP11"/>
+    <mergeCell ref="Q9:Q11"/>
+    <mergeCell ref="BG10:BG11"/>
+    <mergeCell ref="AG9:AG11"/>
+    <mergeCell ref="U9:U11"/>
+    <mergeCell ref="V9:W10"/>
+    <mergeCell ref="X9:X11"/>
+    <mergeCell ref="Y9:Y11"/>
+    <mergeCell ref="Z9:Z11"/>
+    <mergeCell ref="AA9:AA11"/>
+    <mergeCell ref="AB9:AB11"/>
+    <mergeCell ref="AC9:AC11"/>
+    <mergeCell ref="AD9:AD11"/>
+    <mergeCell ref="AE9:AE11"/>
+    <mergeCell ref="AU8:AU11"/>
+    <mergeCell ref="AV8:AV11"/>
+    <mergeCell ref="AW8:AW11"/>
+    <mergeCell ref="R9:R11"/>
+    <mergeCell ref="S9:S11"/>
+    <mergeCell ref="T9:T11"/>
     <mergeCell ref="BX8:CA10"/>
     <mergeCell ref="CB8:CB11"/>
     <mergeCell ref="CC8:CC11"/>
@@ -18111,46 +18152,38 @@
     <mergeCell ref="BT8:BT11"/>
     <mergeCell ref="BU8:BU11"/>
     <mergeCell ref="BW8:BW11"/>
-    <mergeCell ref="BH10:BH11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="AF9:AF11"/>
+    <mergeCell ref="BC10:BC11"/>
+    <mergeCell ref="BD10:BD11"/>
+    <mergeCell ref="BE10:BE11"/>
+    <mergeCell ref="AH9:AH11"/>
+    <mergeCell ref="AI9:AI11"/>
+    <mergeCell ref="AJ9:AJ11"/>
+    <mergeCell ref="AK9:AK11"/>
+    <mergeCell ref="AL9:AL11"/>
+    <mergeCell ref="AM9:AM11"/>
+    <mergeCell ref="AQ8:AQ11"/>
+    <mergeCell ref="AN9:AN11"/>
+    <mergeCell ref="AO9:AO11"/>
     <mergeCell ref="AR8:AR11"/>
     <mergeCell ref="AS8:AS11"/>
     <mergeCell ref="AT8:AT11"/>
-    <mergeCell ref="AU8:AU11"/>
-    <mergeCell ref="AV8:AV11"/>
-    <mergeCell ref="AW8:AW11"/>
-    <mergeCell ref="R9:R11"/>
-    <mergeCell ref="S9:S11"/>
-    <mergeCell ref="T9:T11"/>
+    <mergeCell ref="BS8:BS11"/>
+    <mergeCell ref="BO10:BO11"/>
+    <mergeCell ref="BJ10:BJ11"/>
+    <mergeCell ref="BK10:BK11"/>
+    <mergeCell ref="BL10:BL11"/>
+    <mergeCell ref="BM10:BM11"/>
+    <mergeCell ref="BN10:BN11"/>
+    <mergeCell ref="BP10:BP11"/>
+    <mergeCell ref="AY9:BJ9"/>
+    <mergeCell ref="BK9:BP9"/>
+    <mergeCell ref="BQ9:BQ11"/>
+    <mergeCell ref="BR9:BR11"/>
+    <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="BF10:BF11"/>
-    <mergeCell ref="BG10:BG11"/>
-    <mergeCell ref="AG9:AG11"/>
-    <mergeCell ref="U9:U11"/>
-    <mergeCell ref="V9:W10"/>
-    <mergeCell ref="X9:X11"/>
-    <mergeCell ref="Y9:Y11"/>
-    <mergeCell ref="Z9:Z11"/>
-    <mergeCell ref="AA9:AA11"/>
-    <mergeCell ref="AB9:AB11"/>
-    <mergeCell ref="AC9:AC11"/>
-    <mergeCell ref="AD9:AD11"/>
-    <mergeCell ref="AE9:AE11"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB6"/>
-    <mergeCell ref="A8:A11"/>
-    <mergeCell ref="B8:B11"/>
-    <mergeCell ref="C8:C11"/>
-    <mergeCell ref="D8:D11"/>
-    <mergeCell ref="E8:E11"/>
-    <mergeCell ref="F8:F11"/>
-    <mergeCell ref="G8:G11"/>
-    <mergeCell ref="H8:H11"/>
-    <mergeCell ref="I8:I11"/>
-    <mergeCell ref="J8:J11"/>
-    <mergeCell ref="K8:X8"/>
-    <mergeCell ref="Y8:AO8"/>
-    <mergeCell ref="AP8:AP11"/>
-    <mergeCell ref="Q9:Q11"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B12 C12:BU12 B22:B1048576">
     <cfRule type="duplicateValues" dxfId="12" priority="6"/>
@@ -18384,91 +18417,91 @@
       <c r="CD2" s="137"/>
     </row>
     <row r="3" spans="1:87" s="139" customFormat="1" outlineLevel="1">
-      <c r="A3" s="333" t="str">
+      <c r="A3" s="323" t="str">
         <f ca="1">"BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …."&amp;" NĂM "&amp;YEAR(NOW())</f>
         <v>BẢNG THANH TOÁN TIỀN LƯƠNG THÁNG …. NĂM 2026</v>
       </c>
-      <c r="B3" s="333"/>
-      <c r="C3" s="333"/>
-      <c r="D3" s="333"/>
-      <c r="E3" s="333"/>
-      <c r="F3" s="333"/>
-      <c r="G3" s="333"/>
-      <c r="H3" s="333"/>
-      <c r="I3" s="333"/>
-      <c r="J3" s="333"/>
-      <c r="K3" s="333"/>
-      <c r="L3" s="333"/>
-      <c r="M3" s="333"/>
-      <c r="N3" s="333"/>
-      <c r="O3" s="333"/>
-      <c r="P3" s="333"/>
-      <c r="Q3" s="333"/>
-      <c r="R3" s="333"/>
-      <c r="S3" s="333"/>
-      <c r="T3" s="333"/>
-      <c r="U3" s="333"/>
-      <c r="V3" s="333"/>
-      <c r="W3" s="333"/>
-      <c r="X3" s="333"/>
-      <c r="Y3" s="333"/>
-      <c r="Z3" s="333"/>
-      <c r="AA3" s="333"/>
-      <c r="AB3" s="333"/>
-      <c r="AC3" s="333"/>
-      <c r="AD3" s="333"/>
-      <c r="AE3" s="333"/>
-      <c r="AF3" s="333"/>
-      <c r="AG3" s="333"/>
-      <c r="AH3" s="333"/>
-      <c r="AI3" s="333"/>
-      <c r="AJ3" s="333"/>
-      <c r="AK3" s="333"/>
-      <c r="AL3" s="333"/>
-      <c r="AM3" s="333"/>
-      <c r="AN3" s="333"/>
-      <c r="AO3" s="333"/>
-      <c r="AP3" s="333"/>
-      <c r="AQ3" s="333"/>
-      <c r="AR3" s="333"/>
-      <c r="AS3" s="333"/>
-      <c r="AT3" s="333"/>
-      <c r="AU3" s="333"/>
-      <c r="AV3" s="333"/>
-      <c r="AW3" s="333"/>
-      <c r="AX3" s="333"/>
-      <c r="AY3" s="333"/>
-      <c r="AZ3" s="333"/>
-      <c r="BA3" s="333"/>
-      <c r="BB3" s="333"/>
-      <c r="BC3" s="333"/>
-      <c r="BD3" s="333"/>
-      <c r="BE3" s="333"/>
-      <c r="BF3" s="333"/>
-      <c r="BG3" s="333"/>
-      <c r="BH3" s="333"/>
-      <c r="BI3" s="333"/>
-      <c r="BJ3" s="333"/>
-      <c r="BK3" s="333"/>
-      <c r="BL3" s="333"/>
-      <c r="BM3" s="333"/>
-      <c r="BN3" s="333"/>
-      <c r="BO3" s="333"/>
-      <c r="BP3" s="333"/>
-      <c r="BQ3" s="333"/>
-      <c r="BR3" s="333"/>
-      <c r="BS3" s="333"/>
-      <c r="BT3" s="333"/>
-      <c r="BU3" s="333"/>
+      <c r="B3" s="323"/>
+      <c r="C3" s="323"/>
+      <c r="D3" s="323"/>
+      <c r="E3" s="323"/>
+      <c r="F3" s="323"/>
+      <c r="G3" s="323"/>
+      <c r="H3" s="323"/>
+      <c r="I3" s="323"/>
+      <c r="J3" s="323"/>
+      <c r="K3" s="323"/>
+      <c r="L3" s="323"/>
+      <c r="M3" s="323"/>
+      <c r="N3" s="323"/>
+      <c r="O3" s="323"/>
+      <c r="P3" s="323"/>
+      <c r="Q3" s="323"/>
+      <c r="R3" s="323"/>
+      <c r="S3" s="323"/>
+      <c r="T3" s="323"/>
+      <c r="U3" s="323"/>
+      <c r="V3" s="323"/>
+      <c r="W3" s="323"/>
+      <c r="X3" s="323"/>
+      <c r="Y3" s="323"/>
+      <c r="Z3" s="323"/>
+      <c r="AA3" s="323"/>
+      <c r="AB3" s="323"/>
+      <c r="AC3" s="323"/>
+      <c r="AD3" s="323"/>
+      <c r="AE3" s="323"/>
+      <c r="AF3" s="323"/>
+      <c r="AG3" s="323"/>
+      <c r="AH3" s="323"/>
+      <c r="AI3" s="323"/>
+      <c r="AJ3" s="323"/>
+      <c r="AK3" s="323"/>
+      <c r="AL3" s="323"/>
+      <c r="AM3" s="323"/>
+      <c r="AN3" s="323"/>
+      <c r="AO3" s="323"/>
+      <c r="AP3" s="323"/>
+      <c r="AQ3" s="323"/>
+      <c r="AR3" s="323"/>
+      <c r="AS3" s="323"/>
+      <c r="AT3" s="323"/>
+      <c r="AU3" s="323"/>
+      <c r="AV3" s="323"/>
+      <c r="AW3" s="323"/>
+      <c r="AX3" s="323"/>
+      <c r="AY3" s="323"/>
+      <c r="AZ3" s="323"/>
+      <c r="BA3" s="323"/>
+      <c r="BB3" s="323"/>
+      <c r="BC3" s="323"/>
+      <c r="BD3" s="323"/>
+      <c r="BE3" s="323"/>
+      <c r="BF3" s="323"/>
+      <c r="BG3" s="323"/>
+      <c r="BH3" s="323"/>
+      <c r="BI3" s="323"/>
+      <c r="BJ3" s="323"/>
+      <c r="BK3" s="323"/>
+      <c r="BL3" s="323"/>
+      <c r="BM3" s="323"/>
+      <c r="BN3" s="323"/>
+      <c r="BO3" s="323"/>
+      <c r="BP3" s="323"/>
+      <c r="BQ3" s="323"/>
+      <c r="BR3" s="323"/>
+      <c r="BS3" s="323"/>
+      <c r="BT3" s="323"/>
+      <c r="BU3" s="323"/>
       <c r="BV3"/>
-      <c r="BW3" s="334" t="s">
+      <c r="BW3" s="324" t="s">
         <v>2</v>
       </c>
-      <c r="BX3" s="334"/>
-      <c r="BY3" s="334"/>
-      <c r="BZ3" s="334"/>
-      <c r="CA3" s="334"/>
-      <c r="CB3" s="333"/>
+      <c r="BX3" s="324"/>
+      <c r="BY3" s="324"/>
+      <c r="BZ3" s="324"/>
+      <c r="CA3" s="324"/>
+      <c r="CB3" s="323"/>
       <c r="CC3" s="138"/>
       <c r="CD3" s="138"/>
       <c r="CE3" s="139" t="s">
@@ -18552,368 +18585,368 @@
       <c r="BT4" s="140"/>
       <c r="BU4" s="140"/>
       <c r="BV4"/>
-      <c r="BW4" s="333"/>
-      <c r="BX4" s="333"/>
-      <c r="BY4" s="333"/>
-      <c r="BZ4" s="333"/>
-      <c r="CA4" s="333"/>
-      <c r="CB4" s="333"/>
+      <c r="BW4" s="323"/>
+      <c r="BX4" s="323"/>
+      <c r="BY4" s="323"/>
+      <c r="BZ4" s="323"/>
+      <c r="CA4" s="323"/>
+      <c r="CB4" s="323"/>
       <c r="CC4" s="138"/>
       <c r="CD4" s="138"/>
     </row>
     <row r="5" spans="1:87" s="141" customFormat="1">
-      <c r="A5" s="299" t="s">
+      <c r="A5" s="277" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="302" t="s">
+      <c r="B5" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="245" t="s">
+      <c r="C5" s="256" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="305" t="s">
+      <c r="D5" s="272" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="305" t="s">
+      <c r="E5" s="272" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="340" t="s">
+      <c r="F5" s="348" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="245" t="s">
+      <c r="G5" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="323" t="s">
+      <c r="H5" s="325" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="323" t="s">
+      <c r="I5" s="325" t="s">
         <v>12</v>
       </c>
-      <c r="J5" s="245" t="s">
+      <c r="J5" s="256" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="335" t="s">
+      <c r="K5" s="328" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="336"/>
-      <c r="M5" s="336"/>
-      <c r="N5" s="336"/>
-      <c r="O5" s="336"/>
-      <c r="P5" s="336"/>
-      <c r="Q5" s="336"/>
-      <c r="R5" s="336"/>
-      <c r="S5" s="336"/>
-      <c r="T5" s="336"/>
-      <c r="U5" s="336"/>
-      <c r="V5" s="336"/>
-      <c r="W5" s="336"/>
-      <c r="X5" s="336"/>
-      <c r="Y5" s="337" t="s">
+      <c r="L5" s="329"/>
+      <c r="M5" s="329"/>
+      <c r="N5" s="329"/>
+      <c r="O5" s="329"/>
+      <c r="P5" s="329"/>
+      <c r="Q5" s="329"/>
+      <c r="R5" s="329"/>
+      <c r="S5" s="329"/>
+      <c r="T5" s="329"/>
+      <c r="U5" s="329"/>
+      <c r="V5" s="329"/>
+      <c r="W5" s="329"/>
+      <c r="X5" s="329"/>
+      <c r="Y5" s="330" t="s">
         <v>15</v>
       </c>
-      <c r="Z5" s="338"/>
-      <c r="AA5" s="338"/>
-      <c r="AB5" s="338"/>
-      <c r="AC5" s="338"/>
-      <c r="AD5" s="338"/>
-      <c r="AE5" s="338"/>
-      <c r="AF5" s="338"/>
-      <c r="AG5" s="338"/>
-      <c r="AH5" s="338"/>
-      <c r="AI5" s="338"/>
-      <c r="AJ5" s="338"/>
-      <c r="AK5" s="338"/>
-      <c r="AL5" s="338"/>
-      <c r="AM5" s="338"/>
-      <c r="AN5" s="338"/>
-      <c r="AO5" s="339"/>
-      <c r="AP5" s="245" t="s">
+      <c r="Z5" s="331"/>
+      <c r="AA5" s="331"/>
+      <c r="AB5" s="331"/>
+      <c r="AC5" s="331"/>
+      <c r="AD5" s="331"/>
+      <c r="AE5" s="331"/>
+      <c r="AF5" s="331"/>
+      <c r="AG5" s="331"/>
+      <c r="AH5" s="331"/>
+      <c r="AI5" s="331"/>
+      <c r="AJ5" s="331"/>
+      <c r="AK5" s="331"/>
+      <c r="AL5" s="331"/>
+      <c r="AM5" s="331"/>
+      <c r="AN5" s="331"/>
+      <c r="AO5" s="332"/>
+      <c r="AP5" s="256" t="s">
         <v>16</v>
       </c>
-      <c r="AQ5" s="245" t="s">
+      <c r="AQ5" s="256" t="s">
         <v>17</v>
       </c>
-      <c r="AR5" s="245" t="s">
+      <c r="AR5" s="256" t="s">
         <v>18</v>
       </c>
-      <c r="AS5" s="245" t="s">
+      <c r="AS5" s="256" t="s">
         <v>19</v>
       </c>
-      <c r="AT5" s="245" t="s">
+      <c r="AT5" s="256" t="s">
         <v>20</v>
       </c>
-      <c r="AU5" s="245" t="s">
+      <c r="AU5" s="256" t="s">
         <v>21</v>
       </c>
-      <c r="AV5" s="245" t="s">
+      <c r="AV5" s="256" t="s">
         <v>22</v>
       </c>
-      <c r="AW5" s="245" t="s">
+      <c r="AW5" s="256" t="s">
         <v>23</v>
       </c>
-      <c r="AX5" s="245" t="s">
+      <c r="AX5" s="256" t="s">
         <v>24</v>
       </c>
-      <c r="AY5" s="313" t="s">
+      <c r="AY5" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="AZ5" s="314"/>
-      <c r="BA5" s="314"/>
-      <c r="BB5" s="314"/>
-      <c r="BC5" s="314"/>
-      <c r="BD5" s="314"/>
-      <c r="BE5" s="314"/>
-      <c r="BF5" s="314"/>
-      <c r="BG5" s="314"/>
-      <c r="BH5" s="314"/>
-      <c r="BI5" s="314"/>
-      <c r="BJ5" s="314"/>
-      <c r="BK5" s="314"/>
-      <c r="BL5" s="314"/>
-      <c r="BM5" s="314"/>
-      <c r="BN5" s="314"/>
-      <c r="BO5" s="314"/>
-      <c r="BP5" s="315"/>
-      <c r="BQ5" s="268" t="s">
+      <c r="AZ5" s="260"/>
+      <c r="BA5" s="260"/>
+      <c r="BB5" s="260"/>
+      <c r="BC5" s="260"/>
+      <c r="BD5" s="260"/>
+      <c r="BE5" s="260"/>
+      <c r="BF5" s="260"/>
+      <c r="BG5" s="260"/>
+      <c r="BH5" s="260"/>
+      <c r="BI5" s="260"/>
+      <c r="BJ5" s="260"/>
+      <c r="BK5" s="260"/>
+      <c r="BL5" s="260"/>
+      <c r="BM5" s="260"/>
+      <c r="BN5" s="260"/>
+      <c r="BO5" s="260"/>
+      <c r="BP5" s="261"/>
+      <c r="BQ5" s="315" t="s">
         <v>26</v>
       </c>
-      <c r="BR5" s="275"/>
-      <c r="BS5" s="265" t="s">
+      <c r="BR5" s="322"/>
+      <c r="BS5" s="271" t="s">
         <v>128</v>
       </c>
-      <c r="BT5" s="265" t="s">
+      <c r="BT5" s="271" t="s">
         <v>27</v>
       </c>
-      <c r="BU5" s="268" t="s">
+      <c r="BU5" s="315" t="s">
         <v>28</v>
       </c>
       <c r="BV5"/>
-      <c r="BW5" s="250" t="s">
+      <c r="BW5" s="300" t="s">
         <v>29</v>
       </c>
-      <c r="BX5" s="253" t="s">
+      <c r="BX5" s="303" t="s">
         <v>30</v>
       </c>
-      <c r="BY5" s="254"/>
-      <c r="BZ5" s="254"/>
-      <c r="CA5" s="255"/>
-      <c r="CB5" s="262" t="s">
+      <c r="BY5" s="304"/>
+      <c r="BZ5" s="304"/>
+      <c r="CA5" s="305"/>
+      <c r="CB5" s="312" t="s">
         <v>31</v>
       </c>
-      <c r="CC5" s="242" t="s">
+      <c r="CC5" s="297" t="s">
         <v>32</v>
       </c>
-      <c r="CD5" s="242" t="s">
+      <c r="CD5" s="297" t="s">
         <v>33</v>
       </c>
       <c r="CH5" s="142"/>
       <c r="CI5" s="143"/>
     </row>
     <row r="6" spans="1:87" s="141" customFormat="1">
-      <c r="A6" s="300"/>
-      <c r="B6" s="303"/>
-      <c r="C6" s="246"/>
-      <c r="D6" s="306"/>
-      <c r="E6" s="306"/>
-      <c r="F6" s="341"/>
-      <c r="G6" s="246"/>
-      <c r="H6" s="324"/>
-      <c r="I6" s="324"/>
-      <c r="J6" s="246"/>
-      <c r="K6" s="326" t="s">
+      <c r="A6" s="278"/>
+      <c r="B6" s="281"/>
+      <c r="C6" s="257"/>
+      <c r="D6" s="273"/>
+      <c r="E6" s="273"/>
+      <c r="F6" s="349"/>
+      <c r="G6" s="257"/>
+      <c r="H6" s="326"/>
+      <c r="I6" s="326"/>
+      <c r="J6" s="257"/>
+      <c r="K6" s="333" t="s">
         <v>34</v>
       </c>
-      <c r="L6" s="326" t="s">
+      <c r="L6" s="333" t="s">
         <v>35</v>
       </c>
-      <c r="M6" s="326" t="s">
+      <c r="M6" s="333" t="s">
         <v>36</v>
       </c>
-      <c r="N6" s="326" t="s">
+      <c r="N6" s="333" t="s">
         <v>37</v>
       </c>
-      <c r="O6" s="326" t="s">
+      <c r="O6" s="333" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="326" t="s">
+      <c r="P6" s="333" t="s">
         <v>39</v>
       </c>
-      <c r="Q6" s="326" t="s">
+      <c r="Q6" s="333" t="s">
         <v>40</v>
       </c>
-      <c r="R6" s="326" t="s">
+      <c r="R6" s="333" t="s">
         <v>41</v>
       </c>
-      <c r="S6" s="326" t="s">
+      <c r="S6" s="333" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="326" t="s">
+      <c r="T6" s="333" t="s">
         <v>43</v>
       </c>
-      <c r="U6" s="326" t="s">
+      <c r="U6" s="333" t="s">
         <v>44</v>
       </c>
-      <c r="V6" s="329" t="s">
+      <c r="V6" s="336" t="s">
         <v>45</v>
       </c>
-      <c r="W6" s="330"/>
-      <c r="X6" s="326" t="s">
+      <c r="W6" s="337"/>
+      <c r="X6" s="333" t="s">
         <v>46</v>
       </c>
-      <c r="Y6" s="245" t="s">
+      <c r="Y6" s="256" t="s">
         <v>47</v>
       </c>
-      <c r="Z6" s="245" t="s">
+      <c r="Z6" s="256" t="s">
         <v>48</v>
       </c>
-      <c r="AA6" s="245" t="s">
+      <c r="AA6" s="256" t="s">
         <v>49</v>
       </c>
-      <c r="AB6" s="245" t="s">
+      <c r="AB6" s="256" t="s">
         <v>50</v>
       </c>
-      <c r="AC6" s="323" t="s">
+      <c r="AC6" s="325" t="s">
         <v>51</v>
       </c>
-      <c r="AD6" s="323" t="s">
+      <c r="AD6" s="325" t="s">
         <v>129</v>
       </c>
-      <c r="AE6" s="323" t="s">
+      <c r="AE6" s="325" t="s">
         <v>53</v>
       </c>
-      <c r="AF6" s="323" t="s">
+      <c r="AF6" s="325" t="s">
         <v>54</v>
       </c>
-      <c r="AG6" s="245" t="s">
+      <c r="AG6" s="256" t="s">
         <v>55</v>
       </c>
-      <c r="AH6" s="323" t="s">
+      <c r="AH6" s="325" t="s">
         <v>56</v>
       </c>
-      <c r="AI6" s="323" t="s">
+      <c r="AI6" s="325" t="s">
         <v>57</v>
       </c>
-      <c r="AJ6" s="245" t="s">
+      <c r="AJ6" s="256" t="s">
         <v>58</v>
       </c>
-      <c r="AK6" s="320" t="s">
+      <c r="AK6" s="247" t="s">
         <v>59</v>
       </c>
-      <c r="AL6" s="245" t="s">
+      <c r="AL6" s="256" t="s">
         <v>60</v>
       </c>
-      <c r="AM6" s="245" t="s">
+      <c r="AM6" s="256" t="s">
         <v>61</v>
       </c>
-      <c r="AN6" s="317" t="s">
+      <c r="AN6" s="263" t="s">
         <v>62</v>
       </c>
-      <c r="AO6" s="245" t="s">
+      <c r="AO6" s="256" t="s">
         <v>63</v>
       </c>
-      <c r="AP6" s="246"/>
-      <c r="AQ6" s="246"/>
-      <c r="AR6" s="246"/>
-      <c r="AS6" s="246"/>
-      <c r="AT6" s="246"/>
-      <c r="AU6" s="246"/>
-      <c r="AV6" s="246"/>
-      <c r="AW6" s="246"/>
-      <c r="AX6" s="246"/>
-      <c r="AY6" s="313" t="s">
+      <c r="AP6" s="257"/>
+      <c r="AQ6" s="257"/>
+      <c r="AR6" s="257"/>
+      <c r="AS6" s="257"/>
+      <c r="AT6" s="257"/>
+      <c r="AU6" s="257"/>
+      <c r="AV6" s="257"/>
+      <c r="AW6" s="257"/>
+      <c r="AX6" s="257"/>
+      <c r="AY6" s="259" t="s">
         <v>64</v>
       </c>
-      <c r="AZ6" s="314"/>
-      <c r="BA6" s="314"/>
-      <c r="BB6" s="314"/>
-      <c r="BC6" s="314"/>
-      <c r="BD6" s="314"/>
-      <c r="BE6" s="314"/>
-      <c r="BF6" s="314"/>
-      <c r="BG6" s="314"/>
-      <c r="BH6" s="314"/>
-      <c r="BI6" s="314"/>
-      <c r="BJ6" s="315"/>
-      <c r="BK6" s="313" t="s">
+      <c r="AZ6" s="260"/>
+      <c r="BA6" s="260"/>
+      <c r="BB6" s="260"/>
+      <c r="BC6" s="260"/>
+      <c r="BD6" s="260"/>
+      <c r="BE6" s="260"/>
+      <c r="BF6" s="260"/>
+      <c r="BG6" s="260"/>
+      <c r="BH6" s="260"/>
+      <c r="BI6" s="260"/>
+      <c r="BJ6" s="261"/>
+      <c r="BK6" s="259" t="s">
         <v>65</v>
       </c>
-      <c r="BL6" s="314"/>
-      <c r="BM6" s="314"/>
-      <c r="BN6" s="314"/>
-      <c r="BO6" s="314"/>
-      <c r="BP6" s="315"/>
-      <c r="BQ6" s="266" t="s">
+      <c r="BL6" s="260"/>
+      <c r="BM6" s="260"/>
+      <c r="BN6" s="260"/>
+      <c r="BO6" s="260"/>
+      <c r="BP6" s="261"/>
+      <c r="BQ6" s="269" t="s">
         <v>66</v>
       </c>
-      <c r="BR6" s="266" t="s">
+      <c r="BR6" s="269" t="s">
         <v>67</v>
       </c>
-      <c r="BS6" s="266"/>
-      <c r="BT6" s="266"/>
-      <c r="BU6" s="269"/>
+      <c r="BS6" s="269"/>
+      <c r="BT6" s="269"/>
+      <c r="BU6" s="316"/>
       <c r="BV6"/>
-      <c r="BW6" s="251"/>
-      <c r="BX6" s="256"/>
-      <c r="BY6" s="257"/>
-      <c r="BZ6" s="257"/>
-      <c r="CA6" s="258"/>
-      <c r="CB6" s="263"/>
-      <c r="CC6" s="243"/>
-      <c r="CD6" s="243"/>
+      <c r="BW6" s="301"/>
+      <c r="BX6" s="306"/>
+      <c r="BY6" s="307"/>
+      <c r="BZ6" s="307"/>
+      <c r="CA6" s="308"/>
+      <c r="CB6" s="313"/>
+      <c r="CC6" s="298"/>
+      <c r="CD6" s="298"/>
       <c r="CH6" s="142"/>
       <c r="CI6" s="143"/>
     </row>
     <row r="7" spans="1:87" s="141" customFormat="1">
-      <c r="A7" s="300"/>
-      <c r="B7" s="303"/>
-      <c r="C7" s="246"/>
-      <c r="D7" s="306"/>
-      <c r="E7" s="306"/>
-      <c r="F7" s="341"/>
-      <c r="G7" s="246"/>
-      <c r="H7" s="324"/>
-      <c r="I7" s="324"/>
-      <c r="J7" s="246"/>
-      <c r="K7" s="327"/>
-      <c r="L7" s="327"/>
-      <c r="M7" s="327"/>
-      <c r="N7" s="327"/>
-      <c r="O7" s="327"/>
-      <c r="P7" s="327"/>
-      <c r="Q7" s="327"/>
-      <c r="R7" s="327"/>
-      <c r="S7" s="327"/>
-      <c r="T7" s="327"/>
-      <c r="U7" s="327"/>
-      <c r="V7" s="331"/>
-      <c r="W7" s="332"/>
-      <c r="X7" s="327"/>
-      <c r="Y7" s="246"/>
-      <c r="Z7" s="246"/>
-      <c r="AA7" s="246"/>
-      <c r="AB7" s="246"/>
-      <c r="AC7" s="324"/>
-      <c r="AD7" s="324"/>
-      <c r="AE7" s="324"/>
-      <c r="AF7" s="324"/>
-      <c r="AG7" s="246"/>
-      <c r="AH7" s="324"/>
-      <c r="AI7" s="324"/>
-      <c r="AJ7" s="246"/>
-      <c r="AK7" s="321"/>
-      <c r="AL7" s="246"/>
-      <c r="AM7" s="246"/>
-      <c r="AN7" s="318"/>
-      <c r="AO7" s="246"/>
-      <c r="AP7" s="246"/>
-      <c r="AQ7" s="246"/>
-      <c r="AR7" s="246"/>
-      <c r="AS7" s="246"/>
-      <c r="AT7" s="246"/>
-      <c r="AU7" s="246"/>
-      <c r="AV7" s="246"/>
-      <c r="AW7" s="246"/>
-      <c r="AX7" s="246"/>
+      <c r="A7" s="278"/>
+      <c r="B7" s="281"/>
+      <c r="C7" s="257"/>
+      <c r="D7" s="273"/>
+      <c r="E7" s="273"/>
+      <c r="F7" s="349"/>
+      <c r="G7" s="257"/>
+      <c r="H7" s="326"/>
+      <c r="I7" s="326"/>
+      <c r="J7" s="257"/>
+      <c r="K7" s="334"/>
+      <c r="L7" s="334"/>
+      <c r="M7" s="334"/>
+      <c r="N7" s="334"/>
+      <c r="O7" s="334"/>
+      <c r="P7" s="334"/>
+      <c r="Q7" s="334"/>
+      <c r="R7" s="334"/>
+      <c r="S7" s="334"/>
+      <c r="T7" s="334"/>
+      <c r="U7" s="334"/>
+      <c r="V7" s="338"/>
+      <c r="W7" s="339"/>
+      <c r="X7" s="334"/>
+      <c r="Y7" s="257"/>
+      <c r="Z7" s="257"/>
+      <c r="AA7" s="257"/>
+      <c r="AB7" s="257"/>
+      <c r="AC7" s="326"/>
+      <c r="AD7" s="326"/>
+      <c r="AE7" s="326"/>
+      <c r="AF7" s="326"/>
+      <c r="AG7" s="257"/>
+      <c r="AH7" s="326"/>
+      <c r="AI7" s="326"/>
+      <c r="AJ7" s="257"/>
+      <c r="AK7" s="248"/>
+      <c r="AL7" s="257"/>
+      <c r="AM7" s="257"/>
+      <c r="AN7" s="264"/>
+      <c r="AO7" s="257"/>
+      <c r="AP7" s="257"/>
+      <c r="AQ7" s="257"/>
+      <c r="AR7" s="257"/>
+      <c r="AS7" s="257"/>
+      <c r="AT7" s="257"/>
+      <c r="AU7" s="257"/>
+      <c r="AV7" s="257"/>
+      <c r="AW7" s="257"/>
+      <c r="AX7" s="257"/>
       <c r="AY7" s="101" t="s">
         <v>68</v>
       </c>
@@ -18923,123 +18956,123 @@
       <c r="BA7" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="BB7" s="265" t="s">
+      <c r="BB7" s="271" t="s">
         <v>71</v>
       </c>
-      <c r="BC7" s="248" t="s">
+      <c r="BC7" s="245" t="s">
         <v>72</v>
       </c>
-      <c r="BD7" s="248" t="s">
+      <c r="BD7" s="245" t="s">
         <v>73</v>
       </c>
-      <c r="BE7" s="248" t="s">
+      <c r="BE7" s="245" t="s">
         <v>130</v>
       </c>
-      <c r="BF7" s="248" t="s">
+      <c r="BF7" s="245" t="s">
         <v>75</v>
       </c>
-      <c r="BG7" s="248" t="s">
+      <c r="BG7" s="245" t="s">
         <v>76</v>
       </c>
-      <c r="BH7" s="248" t="s">
+      <c r="BH7" s="245" t="s">
         <v>77</v>
       </c>
-      <c r="BI7" s="248" t="s">
+      <c r="BI7" s="245" t="s">
         <v>80</v>
       </c>
-      <c r="BJ7" s="311" t="s">
+      <c r="BJ7" s="283" t="s">
         <v>81</v>
       </c>
-      <c r="BK7" s="248" t="s">
+      <c r="BK7" s="245" t="s">
         <v>82</v>
       </c>
-      <c r="BL7" s="265" t="s">
+      <c r="BL7" s="271" t="s">
         <v>83</v>
       </c>
-      <c r="BM7" s="248" t="s">
+      <c r="BM7" s="245" t="s">
         <v>84</v>
       </c>
-      <c r="BN7" s="265" t="s">
+      <c r="BN7" s="271" t="s">
         <v>85</v>
       </c>
-      <c r="BO7" s="265" t="s">
+      <c r="BO7" s="271" t="s">
         <v>131</v>
       </c>
-      <c r="BP7" s="265" t="s">
+      <c r="BP7" s="271" t="s">
         <v>86</v>
       </c>
-      <c r="BQ7" s="266"/>
-      <c r="BR7" s="266"/>
-      <c r="BS7" s="266"/>
-      <c r="BT7" s="266"/>
-      <c r="BU7" s="269"/>
+      <c r="BQ7" s="269"/>
+      <c r="BR7" s="269"/>
+      <c r="BS7" s="269"/>
+      <c r="BT7" s="269"/>
+      <c r="BU7" s="316"/>
       <c r="BV7"/>
-      <c r="BW7" s="252"/>
-      <c r="BX7" s="259"/>
-      <c r="BY7" s="260"/>
-      <c r="BZ7" s="260"/>
-      <c r="CA7" s="261"/>
-      <c r="CB7" s="264"/>
-      <c r="CC7" s="244"/>
-      <c r="CD7" s="244"/>
+      <c r="BW7" s="302"/>
+      <c r="BX7" s="309"/>
+      <c r="BY7" s="310"/>
+      <c r="BZ7" s="310"/>
+      <c r="CA7" s="311"/>
+      <c r="CB7" s="314"/>
+      <c r="CC7" s="299"/>
+      <c r="CD7" s="299"/>
       <c r="CH7" s="142"/>
       <c r="CI7" s="143"/>
     </row>
     <row r="8" spans="1:87" s="141" customFormat="1" ht="24">
-      <c r="A8" s="301"/>
-      <c r="B8" s="304"/>
-      <c r="C8" s="247"/>
-      <c r="D8" s="307"/>
-      <c r="E8" s="307"/>
-      <c r="F8" s="342"/>
-      <c r="G8" s="247"/>
-      <c r="H8" s="325"/>
-      <c r="I8" s="325"/>
-      <c r="J8" s="247"/>
-      <c r="K8" s="328"/>
-      <c r="L8" s="328"/>
-      <c r="M8" s="328"/>
-      <c r="N8" s="328"/>
-      <c r="O8" s="328"/>
-      <c r="P8" s="328"/>
-      <c r="Q8" s="328"/>
-      <c r="R8" s="328"/>
-      <c r="S8" s="328"/>
-      <c r="T8" s="328"/>
-      <c r="U8" s="328"/>
+      <c r="A8" s="279"/>
+      <c r="B8" s="282"/>
+      <c r="C8" s="258"/>
+      <c r="D8" s="274"/>
+      <c r="E8" s="274"/>
+      <c r="F8" s="350"/>
+      <c r="G8" s="258"/>
+      <c r="H8" s="327"/>
+      <c r="I8" s="327"/>
+      <c r="J8" s="258"/>
+      <c r="K8" s="335"/>
+      <c r="L8" s="335"/>
+      <c r="M8" s="335"/>
+      <c r="N8" s="335"/>
+      <c r="O8" s="335"/>
+      <c r="P8" s="335"/>
+      <c r="Q8" s="335"/>
+      <c r="R8" s="335"/>
+      <c r="S8" s="335"/>
+      <c r="T8" s="335"/>
+      <c r="U8" s="335"/>
       <c r="V8" s="145" t="s">
         <v>87</v>
       </c>
       <c r="W8" s="145" t="s">
         <v>88</v>
       </c>
-      <c r="X8" s="328"/>
-      <c r="Y8" s="247"/>
-      <c r="Z8" s="247"/>
-      <c r="AA8" s="247"/>
-      <c r="AB8" s="247"/>
-      <c r="AC8" s="325"/>
-      <c r="AD8" s="325"/>
-      <c r="AE8" s="325"/>
-      <c r="AF8" s="325"/>
-      <c r="AG8" s="247"/>
-      <c r="AH8" s="325"/>
-      <c r="AI8" s="325"/>
-      <c r="AJ8" s="247"/>
-      <c r="AK8" s="322"/>
-      <c r="AL8" s="247"/>
-      <c r="AM8" s="247"/>
-      <c r="AN8" s="319"/>
-      <c r="AO8" s="247"/>
-      <c r="AP8" s="247"/>
-      <c r="AQ8" s="247"/>
-      <c r="AR8" s="247"/>
-      <c r="AS8" s="247"/>
-      <c r="AT8" s="247"/>
-      <c r="AU8" s="247"/>
-      <c r="AV8" s="247"/>
-      <c r="AW8" s="247"/>
-      <c r="AX8" s="247"/>
+      <c r="X8" s="335"/>
+      <c r="Y8" s="258"/>
+      <c r="Z8" s="258"/>
+      <c r="AA8" s="258"/>
+      <c r="AB8" s="258"/>
+      <c r="AC8" s="327"/>
+      <c r="AD8" s="327"/>
+      <c r="AE8" s="327"/>
+      <c r="AF8" s="327"/>
+      <c r="AG8" s="258"/>
+      <c r="AH8" s="327"/>
+      <c r="AI8" s="327"/>
+      <c r="AJ8" s="258"/>
+      <c r="AK8" s="249"/>
+      <c r="AL8" s="258"/>
+      <c r="AM8" s="258"/>
+      <c r="AN8" s="265"/>
+      <c r="AO8" s="258"/>
+      <c r="AP8" s="258"/>
+      <c r="AQ8" s="258"/>
+      <c r="AR8" s="258"/>
+      <c r="AS8" s="258"/>
+      <c r="AT8" s="258"/>
+      <c r="AU8" s="258"/>
+      <c r="AV8" s="258"/>
+      <c r="AW8" s="258"/>
+      <c r="AX8" s="258"/>
       <c r="AY8" s="102" t="s">
         <v>89</v>
       </c>
@@ -19049,28 +19082,28 @@
       <c r="BA8" s="102" t="s">
         <v>91</v>
       </c>
-      <c r="BB8" s="267"/>
-      <c r="BC8" s="249"/>
-      <c r="BD8" s="249"/>
-      <c r="BE8" s="249"/>
-      <c r="BF8" s="249"/>
-      <c r="BG8" s="249"/>
-      <c r="BH8" s="249"/>
-      <c r="BI8" s="249"/>
-      <c r="BJ8" s="312"/>
-      <c r="BK8" s="249"/>
-      <c r="BL8" s="267"/>
-      <c r="BM8" s="249"/>
-      <c r="BN8" s="267"/>
-      <c r="BO8" s="267"/>
-      <c r="BP8" s="267"/>
-      <c r="BQ8" s="267"/>
-      <c r="BR8" s="267"/>
-      <c r="BS8" s="267"/>
-      <c r="BT8" s="267"/>
-      <c r="BU8" s="270"/>
+      <c r="BB8" s="270"/>
+      <c r="BC8" s="246"/>
+      <c r="BD8" s="246"/>
+      <c r="BE8" s="246"/>
+      <c r="BF8" s="246"/>
+      <c r="BG8" s="246"/>
+      <c r="BH8" s="246"/>
+      <c r="BI8" s="246"/>
+      <c r="BJ8" s="284"/>
+      <c r="BK8" s="246"/>
+      <c r="BL8" s="270"/>
+      <c r="BM8" s="246"/>
+      <c r="BN8" s="270"/>
+      <c r="BO8" s="270"/>
+      <c r="BP8" s="270"/>
+      <c r="BQ8" s="270"/>
+      <c r="BR8" s="270"/>
+      <c r="BS8" s="270"/>
+      <c r="BT8" s="270"/>
+      <c r="BU8" s="317"/>
       <c r="BV8"/>
-      <c r="BW8" s="252"/>
+      <c r="BW8" s="302"/>
       <c r="BX8" s="72" t="s">
         <v>92</v>
       </c>
@@ -19083,9 +19116,9 @@
       <c r="CA8" s="73" t="s">
         <v>95</v>
       </c>
-      <c r="CB8" s="264"/>
-      <c r="CC8" s="244"/>
-      <c r="CD8" s="244"/>
+      <c r="CB8" s="314"/>
+      <c r="CC8" s="299"/>
+      <c r="CD8" s="299"/>
       <c r="CF8" s="146"/>
       <c r="CH8" s="142"/>
       <c r="CI8" s="143"/>
@@ -21262,24 +21295,54 @@
   <autoFilter ref="A9:CI14" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <dataConsolidate/>
   <mergeCells count="82">
-    <mergeCell ref="BK6:BP6"/>
-    <mergeCell ref="BO7:BO8"/>
-    <mergeCell ref="BP7:BP8"/>
-    <mergeCell ref="BI7:BI8"/>
-    <mergeCell ref="BJ7:BJ8"/>
-    <mergeCell ref="BB7:BB8"/>
-    <mergeCell ref="BC7:BC8"/>
-    <mergeCell ref="BD7:BD8"/>
-    <mergeCell ref="BE7:BE8"/>
-    <mergeCell ref="AM6:AM8"/>
-    <mergeCell ref="AN6:AN8"/>
-    <mergeCell ref="AO6:AO8"/>
-    <mergeCell ref="AY6:BJ6"/>
-    <mergeCell ref="T6:T8"/>
-    <mergeCell ref="U6:U8"/>
-    <mergeCell ref="V6:W7"/>
-    <mergeCell ref="X6:X8"/>
-    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="A3:BU3"/>
+    <mergeCell ref="BW3:CB4"/>
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="B5:B8"/>
+    <mergeCell ref="C5:C8"/>
+    <mergeCell ref="D5:D8"/>
+    <mergeCell ref="E5:E8"/>
+    <mergeCell ref="F5:F8"/>
+    <mergeCell ref="G5:G8"/>
+    <mergeCell ref="H5:H8"/>
+    <mergeCell ref="I5:I8"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="K5:X5"/>
+    <mergeCell ref="Y5:AO5"/>
+    <mergeCell ref="AP5:AP8"/>
+    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="Q6:Q8"/>
+    <mergeCell ref="R6:R8"/>
+    <mergeCell ref="S6:S8"/>
+    <mergeCell ref="CD5:CD8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="L6:L8"/>
+    <mergeCell ref="M6:M8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="O6:O8"/>
+    <mergeCell ref="AX5:AX8"/>
+    <mergeCell ref="AY5:BP5"/>
+    <mergeCell ref="BQ5:BR5"/>
+    <mergeCell ref="BS5:BS8"/>
+    <mergeCell ref="BT5:BT8"/>
+    <mergeCell ref="BU5:BU8"/>
+    <mergeCell ref="BR6:BR8"/>
+    <mergeCell ref="Z6:Z8"/>
+    <mergeCell ref="BW5:BW8"/>
+    <mergeCell ref="AQ5:AQ8"/>
+    <mergeCell ref="AL6:AL8"/>
+    <mergeCell ref="AA6:AA8"/>
+    <mergeCell ref="AB6:AB8"/>
+    <mergeCell ref="AC6:AC8"/>
+    <mergeCell ref="AD6:AD8"/>
+    <mergeCell ref="AE6:AE8"/>
+    <mergeCell ref="AF6:AF8"/>
+    <mergeCell ref="AG6:AG8"/>
+    <mergeCell ref="AH6:AH8"/>
+    <mergeCell ref="AI6:AI8"/>
+    <mergeCell ref="AJ6:AJ8"/>
+    <mergeCell ref="AK6:AK8"/>
+    <mergeCell ref="BQ6:BQ8"/>
     <mergeCell ref="BX5:CA7"/>
     <mergeCell ref="CB5:CB8"/>
     <mergeCell ref="CC5:CC8"/>
@@ -21296,54 +21359,24 @@
     <mergeCell ref="BF7:BF8"/>
     <mergeCell ref="BG7:BG8"/>
     <mergeCell ref="BH7:BH8"/>
-    <mergeCell ref="Z6:Z8"/>
-    <mergeCell ref="BW5:BW8"/>
-    <mergeCell ref="AQ5:AQ8"/>
-    <mergeCell ref="AL6:AL8"/>
-    <mergeCell ref="AA6:AA8"/>
-    <mergeCell ref="AB6:AB8"/>
-    <mergeCell ref="AC6:AC8"/>
-    <mergeCell ref="AD6:AD8"/>
-    <mergeCell ref="AE6:AE8"/>
-    <mergeCell ref="AF6:AF8"/>
-    <mergeCell ref="AG6:AG8"/>
-    <mergeCell ref="AH6:AH8"/>
-    <mergeCell ref="AI6:AI8"/>
-    <mergeCell ref="AJ6:AJ8"/>
-    <mergeCell ref="AK6:AK8"/>
-    <mergeCell ref="BQ6:BQ8"/>
-    <mergeCell ref="Q6:Q8"/>
-    <mergeCell ref="R6:R8"/>
-    <mergeCell ref="S6:S8"/>
-    <mergeCell ref="CD5:CD8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="L6:L8"/>
-    <mergeCell ref="M6:M8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="O6:O8"/>
-    <mergeCell ref="AX5:AX8"/>
-    <mergeCell ref="AY5:BP5"/>
-    <mergeCell ref="BQ5:BR5"/>
-    <mergeCell ref="BS5:BS8"/>
-    <mergeCell ref="BT5:BT8"/>
-    <mergeCell ref="BU5:BU8"/>
-    <mergeCell ref="BR6:BR8"/>
-    <mergeCell ref="A3:BU3"/>
-    <mergeCell ref="BW3:CB4"/>
-    <mergeCell ref="A5:A8"/>
-    <mergeCell ref="B5:B8"/>
-    <mergeCell ref="C5:C8"/>
-    <mergeCell ref="D5:D8"/>
-    <mergeCell ref="E5:E8"/>
-    <mergeCell ref="F5:F8"/>
-    <mergeCell ref="G5:G8"/>
-    <mergeCell ref="H5:H8"/>
-    <mergeCell ref="I5:I8"/>
-    <mergeCell ref="J5:J8"/>
-    <mergeCell ref="K5:X5"/>
-    <mergeCell ref="Y5:AO5"/>
-    <mergeCell ref="AP5:AP8"/>
-    <mergeCell ref="P6:P8"/>
+    <mergeCell ref="T6:T8"/>
+    <mergeCell ref="U6:U8"/>
+    <mergeCell ref="V6:W7"/>
+    <mergeCell ref="X6:X8"/>
+    <mergeCell ref="Y6:Y8"/>
+    <mergeCell ref="BB7:BB8"/>
+    <mergeCell ref="BC7:BC8"/>
+    <mergeCell ref="BD7:BD8"/>
+    <mergeCell ref="BE7:BE8"/>
+    <mergeCell ref="AM6:AM8"/>
+    <mergeCell ref="AN6:AN8"/>
+    <mergeCell ref="AO6:AO8"/>
+    <mergeCell ref="AY6:BJ6"/>
+    <mergeCell ref="BK6:BP6"/>
+    <mergeCell ref="BO7:BO8"/>
+    <mergeCell ref="BP7:BP8"/>
+    <mergeCell ref="BI7:BI8"/>
+    <mergeCell ref="BJ7:BJ8"/>
   </mergeCells>
   <conditionalFormatting sqref="B1:B9 B12:B16 C9:BU9 B20:B1048576">
     <cfRule type="duplicateValues" dxfId="6" priority="63"/>
@@ -21356,8 +21389,8 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="B19">
     <cfRule type="duplicateValues" dxfId="3" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="BJ10">
     <cfRule type="duplicateValues" dxfId="0" priority="4"/>
